--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t>ID</t>
   </si>
@@ -657,7 +657,7 @@
     <t>08.674.752/0001-40</t>
   </si>
   <si>
-    <t>68 %</t>
+    <t>84 %</t>
   </si>
   <si>
     <t>APOLO HOSPITALAR</t>
@@ -900,6 +900,9 @@
     <t>Região04</t>
   </si>
   <si>
+    <t>30 %</t>
+  </si>
+  <si>
     <t>MEDICAL MERCANTIL</t>
   </si>
   <si>
@@ -997,6 +1000,18 @@
   </si>
   <si>
     <t>46.359.681/0001-80</t>
+  </si>
+  <si>
+    <t>FLEX HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>FLEX HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>03.606.635/0001-25</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1205,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -3568,7 +3583,7 @@
         <v>14020</v>
       </c>
       <c r="S42" s="7" t="n">
-        <v>9533.6</v>
+        <v>11776.8</v>
       </c>
       <c r="T42" s="4" t="s">
         <v>30</v>
@@ -4729,7 +4744,7 @@
       <c r="L63" s="11"/>
       <c r="M63" s="11"/>
       <c r="N63" s="9" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="O63" s="10" t="n">
         <v>46231.629427465</v>
@@ -4762,30 +4777,30 @@
         <v>21</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="4" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="O64" s="6" t="n">
         <v>46232.365431516</v>
@@ -4800,7 +4815,7 @@
         <v>336168</v>
       </c>
       <c r="S64" s="7" t="n">
-        <v>0</v>
+        <v>99360</v>
       </c>
       <c r="T64" s="4" t="s">
         <v>30</v>
@@ -4818,30 +4833,30 @@
         <v>21</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H65" s="11" t="n">
         <v>46231</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" s="11"/>
       <c r="N65" s="9" t="s">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="O65" s="10" t="n">
         <v>46232.37670934</v>
@@ -4856,7 +4871,7 @@
         <v>4806</v>
       </c>
       <c r="S65" s="12" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="T65" s="9" t="s">
         <v>30</v>
@@ -4880,7 +4895,7 @@
         <v>264</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H66" s="5" t="n">
         <v>46230</v>
@@ -4936,7 +4951,7 @@
         <v>194</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H67" s="11" t="n">
         <v>46231</v>
@@ -4989,10 +5004,10 @@
         <v>198</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H68" s="5" t="n">
         <v>46230</v>
@@ -5045,22 +5060,22 @@
         <v>198</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H69" s="11" t="n">
         <v>46231</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L69" s="11"/>
       <c r="M69" s="11"/>
@@ -5101,22 +5116,22 @@
         <v>22</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
@@ -5154,30 +5169,30 @@
         <v>21</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H71" s="11" t="n">
         <v>46230</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" s="11"/>
       <c r="N71" s="9" t="s">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="O71" s="10" t="n">
         <v>46232.407563194</v>
@@ -5192,7 +5207,7 @@
         <v>8200</v>
       </c>
       <c r="S71" s="12" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="T71" s="9" t="s">
         <v>30</v>
@@ -5213,22 +5228,22 @@
         <v>22</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H72" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
@@ -5269,22 +5284,22 @@
         <v>198</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H73" s="11" t="n">
         <v>46230</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="11"/>
@@ -5310,33 +5325,89 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A74" s="13" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="14"/>
-      <c r="Q74" s="14"/>
-      <c r="R74" s="15" t="n">
-        <v>2104810.3876</v>
-      </c>
-      <c r="S74" s="15" t="n">
-        <v>1328275.81</v>
-      </c>
-      <c r="T74" s="16"/>
+    <row r="74" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A74" s="3" t="n">
+        <v>935</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74" s="6" t="n">
+        <v>46232.457877465</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q74" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R74" s="7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S74" s="7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T74" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A75" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="14"/>
+      <c r="P75" s="14"/>
+      <c r="Q75" s="14"/>
+      <c r="R75" s="15" t="n">
+        <v>2146810.3876</v>
+      </c>
+      <c r="S75" s="15" t="n">
+        <v>1484885.01</v>
+      </c>
+      <c r="T75" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="1841">
   <si>
     <t>ID</t>
   </si>
@@ -3957,7 +3957,7 @@
     <t>04.112.864/0001-56</t>
   </si>
   <si>
-    <t>75 %</t>
+    <t>78 %</t>
   </si>
   <si>
     <t>724</t>
@@ -5487,7 +5487,7 @@
     <t>1100</t>
   </si>
   <si>
-    <t>54 %</t>
+    <t>64 %</t>
   </si>
   <si>
     <t>1101</t>
@@ -5533,6 +5533,9 @@
   </si>
   <si>
     <t>20.001.049/0001-76</t>
+  </si>
+  <si>
+    <t>1111</t>
   </si>
 </sst>
 </file>
@@ -5726,7 +5729,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:T881"/>
+  <dimension ref="A1:T882"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -37166,7 +37169,7 @@
         <v>242444.07</v>
       </c>
       <c r="S561" s="12" t="n">
-        <v>181247.22</v>
+        <v>190038.42</v>
       </c>
       <c r="T561" s="9" t="s">
         <v>30</v>
@@ -54152,7 +54155,7 @@
         <v>21</v>
       </c>
       <c r="E865" s="8" t="s">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="F865" s="9" t="s">
         <v>1813</v>
@@ -54175,7 +54178,7 @@
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
       <c r="N865" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O865" s="11" t="n">
         <v>46232.411495914</v>
@@ -54190,7 +54193,7 @@
         <v>5888.82</v>
       </c>
       <c r="S865" s="12" t="n">
-        <v>0</v>
+        <v>5888.82</v>
       </c>
       <c r="T865" s="9" t="s">
         <v>30</v>
@@ -54582,7 +54585,7 @@
         <v>31208</v>
       </c>
       <c r="S872" s="7" t="n">
-        <v>16804.8</v>
+        <v>20008</v>
       </c>
       <c r="T872" s="4" t="s">
         <v>30</v>
@@ -54936,7 +54939,7 @@
         <v>21</v>
       </c>
       <c r="E879" s="8" t="s">
-        <v>282</v>
+        <v>1314</v>
       </c>
       <c r="F879" s="9" t="s">
         <v>1472</v>
@@ -54974,7 +54977,7 @@
         <v>4083.2</v>
       </c>
       <c r="S879" s="12" t="n">
-        <v>0</v>
+        <v>3203.2</v>
       </c>
       <c r="T879" s="9" t="s">
         <v>30</v>
@@ -55036,33 +55039,89 @@
         <v>30</v>
       </c>
     </row>
-    <row r="881" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A881" s="13" t="n">
-        <v>879</v>
-      </c>
-      <c r="B881" s="14"/>
-      <c r="C881" s="14"/>
-      <c r="D881" s="14"/>
-      <c r="E881" s="14"/>
-      <c r="F881" s="14"/>
-      <c r="G881" s="14"/>
-      <c r="H881" s="14"/>
-      <c r="I881" s="14"/>
-      <c r="J881" s="14"/>
-      <c r="K881" s="14"/>
-      <c r="L881" s="14"/>
-      <c r="M881" s="14"/>
-      <c r="N881" s="14"/>
-      <c r="O881" s="14"/>
-      <c r="P881" s="14"/>
-      <c r="Q881" s="14"/>
-      <c r="R881" s="15" t="n">
-        <v>55556610.5126</v>
-      </c>
-      <c r="S881" s="15" t="n">
-        <v>53650781.285</v>
-      </c>
-      <c r="T881" s="16"/>
+    <row r="881" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A881" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="B881" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C881" s="9"/>
+      <c r="D881" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E881" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F881" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G881" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H881" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I881" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="J881" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K881" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="L881" s="10"/>
+      <c r="M881" s="10"/>
+      <c r="N881" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O881" s="11" t="n">
+        <v>46234.504198461</v>
+      </c>
+      <c r="P881" s="9" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q881" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R881" s="12" t="n">
+        <v>73636</v>
+      </c>
+      <c r="S881" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T881" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="882" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A882" s="13" t="n">
+        <v>880</v>
+      </c>
+      <c r="B882" s="14"/>
+      <c r="C882" s="14"/>
+      <c r="D882" s="14"/>
+      <c r="E882" s="14"/>
+      <c r="F882" s="14"/>
+      <c r="G882" s="14"/>
+      <c r="H882" s="14"/>
+      <c r="I882" s="14"/>
+      <c r="J882" s="14"/>
+      <c r="K882" s="14"/>
+      <c r="L882" s="14"/>
+      <c r="M882" s="14"/>
+      <c r="N882" s="14"/>
+      <c r="O882" s="14"/>
+      <c r="P882" s="14"/>
+      <c r="Q882" s="14"/>
+      <c r="R882" s="15" t="n">
+        <v>55630246.5126</v>
+      </c>
+      <c r="S882" s="15" t="n">
+        <v>53671867.705</v>
+      </c>
+      <c r="T882" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="1841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1843">
   <si>
     <t>ID</t>
   </si>
@@ -3957,1566 +3957,1569 @@
     <t>04.112.864/0001-56</t>
   </si>
   <si>
+    <t>75 %</t>
+  </si>
+  <si>
+    <t>724</t>
+  </si>
+  <si>
+    <t>D ARAUJO</t>
+  </si>
+  <si>
+    <t>726</t>
+  </si>
+  <si>
+    <t>MEDLOG</t>
+  </si>
+  <si>
+    <t>727</t>
+  </si>
+  <si>
+    <t>MEDLOG LTDA</t>
+  </si>
+  <si>
+    <t>41.751.726/0001-43</t>
+  </si>
+  <si>
+    <t>728</t>
+  </si>
+  <si>
+    <t>PHARMAPLUS LTDA</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>733</t>
+  </si>
+  <si>
+    <t>APOLO HOSPITALAR</t>
+  </si>
+  <si>
+    <t>734</t>
+  </si>
+  <si>
+    <t>APOLO H. DISTRIBUICAO C. IMPORTACAO E E. LTDA</t>
+  </si>
+  <si>
+    <t>13.917.345/0001-56</t>
+  </si>
+  <si>
+    <t>735</t>
+  </si>
+  <si>
+    <t>736</t>
+  </si>
+  <si>
+    <t>737</t>
+  </si>
+  <si>
+    <t>738</t>
+  </si>
+  <si>
+    <t>739</t>
+  </si>
+  <si>
+    <t>741</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA MAXIMUS</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE MEDICAMENTOS MAXIMUS LTDA</t>
+  </si>
+  <si>
+    <t>08.563.277/0001-34</t>
+  </si>
+  <si>
+    <t>743</t>
+  </si>
+  <si>
+    <t>LIVMED MATERIAIS</t>
+  </si>
+  <si>
+    <t>744</t>
+  </si>
+  <si>
+    <t>745</t>
+  </si>
+  <si>
+    <t>EUROMED COMERCIO</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>747</t>
+  </si>
+  <si>
+    <t>749</t>
+  </si>
+  <si>
+    <t>752</t>
+  </si>
+  <si>
+    <t>754</t>
+  </si>
+  <si>
+    <t>756</t>
+  </si>
+  <si>
+    <t>757</t>
+  </si>
+  <si>
+    <t>CRALAB SAUDE</t>
+  </si>
+  <si>
+    <t>758</t>
+  </si>
+  <si>
+    <t>759</t>
+  </si>
+  <si>
+    <t>761</t>
+  </si>
+  <si>
+    <t>763</t>
+  </si>
+  <si>
+    <t>764</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
+    <t>767</t>
+  </si>
+  <si>
+    <t>768</t>
+  </si>
+  <si>
+    <t>769</t>
+  </si>
+  <si>
+    <t>770</t>
+  </si>
+  <si>
+    <t>D ARAUJO COMERCIO</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>MAPEMI BRASIL</t>
+  </si>
+  <si>
+    <t>775</t>
+  </si>
+  <si>
+    <t>MAPEMI - BRASIL DISTRIBUICAO E LOGISTICA FARMACEUTICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEMI - BRASIL MATERIAIS MEDICOS E ODONTOLOGICOS </t>
+  </si>
+  <si>
+    <t>84.487.131/0001-35</t>
+  </si>
+  <si>
+    <t>777</t>
+  </si>
+  <si>
+    <t>SABRINA MARTHA</t>
+  </si>
+  <si>
+    <t>779</t>
+  </si>
+  <si>
+    <t>780</t>
+  </si>
+  <si>
+    <t>781</t>
+  </si>
+  <si>
+    <t>782</t>
+  </si>
+  <si>
+    <t>T J FEITOSA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>783</t>
+  </si>
+  <si>
+    <t>784</t>
+  </si>
+  <si>
+    <t>785</t>
+  </si>
+  <si>
+    <t>787</t>
+  </si>
+  <si>
+    <t>788</t>
+  </si>
+  <si>
+    <t>791</t>
+  </si>
+  <si>
+    <t>792</t>
+  </si>
+  <si>
+    <t>794</t>
+  </si>
+  <si>
+    <t>795</t>
+  </si>
+  <si>
+    <t>796</t>
+  </si>
+  <si>
+    <t>797</t>
+  </si>
+  <si>
+    <t>798</t>
+  </si>
+  <si>
+    <t>799</t>
+  </si>
+  <si>
+    <t>VITALLIS DIAGNOSTICA</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>VITALLIS DIAGNOSTICA LTDA</t>
+  </si>
+  <si>
+    <t>01.663.156/0001-15</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>J R BASTOS</t>
+  </si>
+  <si>
+    <t>803</t>
+  </si>
+  <si>
+    <t>14 %</t>
+  </si>
+  <si>
+    <t>804</t>
+  </si>
+  <si>
+    <t>73 %</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>807</t>
+  </si>
+  <si>
+    <t>808</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>813</t>
+  </si>
+  <si>
+    <t>814</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO</t>
+  </si>
+  <si>
+    <t>815</t>
+  </si>
+  <si>
+    <t>816</t>
+  </si>
+  <si>
+    <t>817</t>
+  </si>
+  <si>
+    <t>818</t>
+  </si>
+  <si>
+    <t>CAMEDIC</t>
+  </si>
+  <si>
+    <t>819</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRELI</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
+  </si>
+  <si>
+    <t>28.450.020/0001-83</t>
+  </si>
+  <si>
+    <t>E.R.M COMERCIO</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>E.R.M COMERCIO E SERVICOS</t>
+  </si>
+  <si>
+    <t>E. R. M. DE SOUZA LTDA</t>
+  </si>
+  <si>
+    <t>31.597.128/0001-08</t>
+  </si>
+  <si>
+    <t>821</t>
+  </si>
+  <si>
+    <t>MEDLIFE PRODUTOS</t>
+  </si>
+  <si>
+    <t>822</t>
+  </si>
+  <si>
+    <t>MEDLIFE PRODUTOS MEDICO-HOSPITALARES</t>
+  </si>
+  <si>
+    <t>MEDLIFE PRODUTOS MEDICO-HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>45.772.861/0001-26</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>826</t>
+  </si>
+  <si>
+    <t>827</t>
+  </si>
+  <si>
+    <t>MAIS MED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>829</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>832</t>
+  </si>
+  <si>
+    <t>833</t>
+  </si>
+  <si>
+    <t>834</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>836</t>
+  </si>
+  <si>
+    <t>837</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
+    <t>839</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>MERCANTE HOSPITALAR</t>
+  </si>
+  <si>
+    <t>852</t>
+  </si>
+  <si>
+    <t>MERCANTE DISTRIBUIDOR HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>51.793.632/0001-90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrey    </t>
+  </si>
+  <si>
+    <t>853</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>859</t>
+  </si>
+  <si>
+    <t>COMPRATES COMERCIAL</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>COMPRATES COMERCIAL FARMACEUTICA E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>COMPRATES COMERCIAL FARMACEUTICA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>96.845.896/0001-89</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSP.</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>CIDALAB COMERCIO</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>FARMAGUEDES COMERCIO</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>D &amp; V COMERCIO</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>D &amp; V COMERCIO DE MATERIAL HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>05.964.983/0001-08</t>
+  </si>
+  <si>
+    <t>V L R LIMA</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>J.J DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>J.J DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>07.187.827/0001-03</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>878</t>
+  </si>
+  <si>
+    <t>BIOMED MATERIAIS</t>
+  </si>
+  <si>
+    <t>879</t>
+  </si>
+  <si>
+    <t>59 %</t>
+  </si>
+  <si>
+    <t>880</t>
+  </si>
+  <si>
+    <t>881</t>
+  </si>
+  <si>
+    <t>44 %</t>
+  </si>
+  <si>
+    <t>884</t>
+  </si>
+  <si>
+    <t>MEDFASP SERVICOS &amp; COMERCIO</t>
+  </si>
+  <si>
+    <t>885</t>
+  </si>
+  <si>
+    <t>90 %</t>
+  </si>
+  <si>
+    <t>R5 SOLUCOES</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>86 %</t>
+  </si>
+  <si>
+    <t>887</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>F R HOSPITALAR MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>891</t>
+  </si>
+  <si>
+    <t>892</t>
+  </si>
+  <si>
+    <t>893</t>
+  </si>
+  <si>
+    <t>DL MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>DL MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>48.058.173/0001-97</t>
+  </si>
+  <si>
+    <t>A INICIAR</t>
+  </si>
+  <si>
+    <t>895</t>
+  </si>
+  <si>
+    <t>896</t>
+  </si>
+  <si>
+    <t>4M BR COMERCIO</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>898</t>
+  </si>
+  <si>
+    <t>52 %</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>902</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO</t>
+  </si>
+  <si>
+    <t>903</t>
+  </si>
+  <si>
+    <t>97 %</t>
+  </si>
+  <si>
+    <t>904</t>
+  </si>
+  <si>
+    <t>905</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA RN</t>
+  </si>
+  <si>
+    <t>906</t>
+  </si>
+  <si>
+    <t>907</t>
+  </si>
+  <si>
+    <t>908</t>
+  </si>
+  <si>
+    <t>909</t>
+  </si>
+  <si>
+    <t>910</t>
+  </si>
+  <si>
+    <t>PROMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>911</t>
+  </si>
+  <si>
+    <t>912</t>
+  </si>
+  <si>
+    <t>46 %</t>
+  </si>
+  <si>
+    <t>913</t>
+  </si>
+  <si>
+    <t>914</t>
+  </si>
+  <si>
+    <t>915</t>
+  </si>
+  <si>
+    <t>916</t>
+  </si>
+  <si>
+    <t>917</t>
+  </si>
+  <si>
+    <t>918</t>
+  </si>
+  <si>
+    <t>919</t>
+  </si>
+  <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>921</t>
+  </si>
+  <si>
+    <t>LOPES BARRETO</t>
+  </si>
+  <si>
+    <t>922</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>DIST. RIO PARNAIBA</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
+    <t>D. ARAUJO</t>
+  </si>
+  <si>
+    <t>926</t>
+  </si>
+  <si>
+    <t>927</t>
+  </si>
+  <si>
+    <t>ENDOMED COMERCIO</t>
+  </si>
+  <si>
+    <t>928</t>
+  </si>
+  <si>
+    <t>929</t>
+  </si>
+  <si>
+    <t>HOSP CENTER</t>
+  </si>
+  <si>
+    <t>931</t>
+  </si>
+  <si>
+    <t>HOSP CENTER COMERCIO DE PRODUTOS ODONTO-MEDICO-HOS</t>
+  </si>
+  <si>
+    <t>16.642.091/0001-07</t>
+  </si>
+  <si>
+    <t>932</t>
+  </si>
+  <si>
+    <t>933</t>
+  </si>
+  <si>
+    <t>934</t>
+  </si>
+  <si>
+    <t>935</t>
+  </si>
+  <si>
+    <t>MERCOSUL DIST.</t>
+  </si>
+  <si>
+    <t>936</t>
+  </si>
+  <si>
+    <t>MERCOSUL DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>MERCOSUL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>28.973.504/0001-07</t>
+  </si>
+  <si>
+    <t>937</t>
+  </si>
+  <si>
+    <t>938</t>
+  </si>
+  <si>
+    <t>939</t>
+  </si>
+  <si>
+    <t>940</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>942</t>
+  </si>
+  <si>
+    <t>943</t>
+  </si>
+  <si>
+    <t>RF PRODUTOS HOSPITALARES</t>
+  </si>
+  <si>
+    <t>944</t>
+  </si>
+  <si>
+    <t>945</t>
+  </si>
+  <si>
+    <t>VAL MED PRODUTOS E EQUIP.</t>
+  </si>
+  <si>
+    <t>946</t>
+  </si>
+  <si>
+    <t>947</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>D. ARAUJO COMERCIO</t>
+  </si>
+  <si>
+    <t>951</t>
+  </si>
+  <si>
+    <t>953</t>
+  </si>
+  <si>
+    <t>MERCANTE DISTRIBUIDOR HOSP.</t>
+  </si>
+  <si>
+    <t>954</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>956</t>
+  </si>
+  <si>
+    <t>BANDEIRANTES LAB</t>
+  </si>
+  <si>
+    <t>957</t>
+  </si>
+  <si>
+    <t>LABAND</t>
+  </si>
+  <si>
+    <t>BANDEIRANTES LAB PROD FARMACEUTICOS E HOSPITALARES</t>
+  </si>
+  <si>
+    <t>70.027.479/0001-35</t>
+  </si>
+  <si>
+    <t>958</t>
+  </si>
+  <si>
+    <t>959</t>
+  </si>
+  <si>
+    <t>70 %</t>
+  </si>
+  <si>
+    <t>JFB DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSP</t>
+  </si>
+  <si>
+    <t>963</t>
+  </si>
+  <si>
+    <t>964</t>
+  </si>
+  <si>
+    <t>965</t>
+  </si>
+  <si>
+    <t>966</t>
+  </si>
+  <si>
+    <t>967</t>
+  </si>
+  <si>
+    <t>968</t>
+  </si>
+  <si>
+    <t>HOSPMED - PIAUI</t>
+  </si>
+  <si>
+    <t>969</t>
+  </si>
+  <si>
+    <t>HOSPMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>HOSPMED LTDA</t>
+  </si>
+  <si>
+    <t>00.156.820/0001-77</t>
+  </si>
+  <si>
+    <t>60 %</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>82 %</t>
+  </si>
+  <si>
+    <t>973</t>
+  </si>
+  <si>
+    <t>974</t>
+  </si>
+  <si>
+    <t>UNI-RIM UNIDADE</t>
+  </si>
+  <si>
+    <t>975</t>
+  </si>
+  <si>
+    <t>UNI-RIM UNIDADE DE DOENCAS RENAIS</t>
+  </si>
+  <si>
+    <t>MARCELO BARBOSA LEITE</t>
+  </si>
+  <si>
+    <t>02.553.837/0001-93</t>
+  </si>
+  <si>
+    <t>ULTRA TEXTIL</t>
+  </si>
+  <si>
+    <t>976</t>
+  </si>
+  <si>
+    <t>ALYNE FARMA</t>
+  </si>
+  <si>
+    <t>977</t>
+  </si>
+  <si>
+    <t>FARMACIAS CLARA POPULAR</t>
+  </si>
+  <si>
+    <t>ALYNE FARMA LTDA</t>
+  </si>
+  <si>
+    <t>14.674.114/0001-21</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>979</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>982</t>
+  </si>
+  <si>
+    <t>MED &amp; FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
+    <t>J LAERCIO</t>
+  </si>
+  <si>
+    <t>984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabio     </t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>47 %</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>989</t>
+  </si>
+  <si>
+    <t>89 %</t>
+  </si>
+  <si>
+    <t>EXPRESS DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>992</t>
+  </si>
+  <si>
+    <t>996</t>
+  </si>
+  <si>
+    <t>77 %</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>85 %</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>T S DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>43 %</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>53 %</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>PB MED</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>39 %</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>14.416.886/0001-63</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>GM FARMA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>81 %</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>C G FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>ALTAMED</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>21.581.445/0001-82</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO</t>
+  </si>
+  <si>
+    <t>Região03</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>FERMATA</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>66.175.139/0001-84</t>
+  </si>
+  <si>
+    <t>RC HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>26.147.597/0001-95</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>05.003.408/0001-30</t>
+  </si>
+  <si>
+    <t>PLENA DIST - RN</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>PLENA DIST - PE</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>CIRURGICA SHALOM</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>MP COMERCIO</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>38 %</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>MONTEBELLO</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>08.674.752/0001-40</t>
+  </si>
+  <si>
+    <t>84 %</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>D FARIAS LIMA</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>EXPRESS DIST.</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>83 %</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>1068</t>
+  </si>
+  <si>
+    <t>LS MATERIAIS (HELDER WALNER)</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>A M FARMA - MA</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>A M FARMA - PI</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL MEDICO</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>64.190.875/0001-86</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>39.324.410/0001-23</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>36 %</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>35 %</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>32.658.023/0001-84</t>
+  </si>
+  <si>
+    <t>13 %</t>
+  </si>
+  <si>
+    <t>CONQUISTA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>12.418.191/0001-95</t>
+  </si>
+  <si>
+    <t>30 %</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>F MELO</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>C J A PARENTE</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>83.646.307/0001-91</t>
+  </si>
+  <si>
+    <t>NORTE GREEN</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
+  </si>
+  <si>
+    <t>24.218.223/0001-98</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>46.359.681/0001-80</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL</t>
+  </si>
+  <si>
+    <t>1099</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>64 %</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>61 %</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA DE MED.</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
     <t>78 %</t>
   </si>
   <si>
-    <t>724</t>
-  </si>
-  <si>
-    <t>D ARAUJO</t>
-  </si>
-  <si>
-    <t>726</t>
-  </si>
-  <si>
-    <t>MEDLOG</t>
-  </si>
-  <si>
-    <t>727</t>
-  </si>
-  <si>
-    <t>MEDLOG LTDA</t>
-  </si>
-  <si>
-    <t>41.751.726/0001-43</t>
-  </si>
-  <si>
-    <t>728</t>
-  </si>
-  <si>
-    <t>PHARMAPLUS LTDA</t>
-  </si>
-  <si>
-    <t>732</t>
-  </si>
-  <si>
-    <t>733</t>
-  </si>
-  <si>
-    <t>APOLO HOSPITALAR</t>
-  </si>
-  <si>
-    <t>734</t>
-  </si>
-  <si>
-    <t>APOLO H. DISTRIBUICAO C. IMPORTACAO E E. LTDA</t>
-  </si>
-  <si>
-    <t>13.917.345/0001-56</t>
-  </si>
-  <si>
-    <t>735</t>
-  </si>
-  <si>
-    <t>736</t>
-  </si>
-  <si>
-    <t>737</t>
-  </si>
-  <si>
-    <t>738</t>
-  </si>
-  <si>
-    <t>739</t>
-  </si>
-  <si>
-    <t>741</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA MAXIMUS</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA DE MEDICAMENTOS MAXIMUS LTDA</t>
-  </si>
-  <si>
-    <t>08.563.277/0001-34</t>
-  </si>
-  <si>
-    <t>743</t>
-  </si>
-  <si>
-    <t>LIVMED MATERIAIS</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>745</t>
-  </si>
-  <si>
-    <t>EUROMED COMERCIO</t>
-  </si>
-  <si>
-    <t>746</t>
-  </si>
-  <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>749</t>
-  </si>
-  <si>
-    <t>752</t>
-  </si>
-  <si>
-    <t>754</t>
-  </si>
-  <si>
-    <t>756</t>
-  </si>
-  <si>
-    <t>757</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE</t>
-  </si>
-  <si>
-    <t>758</t>
-  </si>
-  <si>
-    <t>759</t>
-  </si>
-  <si>
-    <t>761</t>
-  </si>
-  <si>
-    <t>763</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
-    <t>766</t>
-  </si>
-  <si>
-    <t>767</t>
-  </si>
-  <si>
-    <t>768</t>
-  </si>
-  <si>
-    <t>769</t>
-  </si>
-  <si>
-    <t>770</t>
-  </si>
-  <si>
-    <t>D ARAUJO COMERCIO</t>
-  </si>
-  <si>
-    <t>772</t>
-  </si>
-  <si>
-    <t>MAPEMI BRASIL</t>
-  </si>
-  <si>
-    <t>775</t>
-  </si>
-  <si>
-    <t>MAPEMI - BRASIL DISTRIBUICAO E LOGISTICA FARMACEUTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEMI - BRASIL MATERIAIS MEDICOS E ODONTOLOGICOS </t>
-  </si>
-  <si>
-    <t>84.487.131/0001-35</t>
-  </si>
-  <si>
-    <t>777</t>
-  </si>
-  <si>
-    <t>SABRINA MARTHA</t>
-  </si>
-  <si>
-    <t>779</t>
-  </si>
-  <si>
-    <t>780</t>
-  </si>
-  <si>
-    <t>781</t>
-  </si>
-  <si>
-    <t>782</t>
-  </si>
-  <si>
-    <t>T J FEITOSA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>783</t>
-  </si>
-  <si>
-    <t>784</t>
-  </si>
-  <si>
-    <t>785</t>
-  </si>
-  <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>788</t>
-  </si>
-  <si>
-    <t>791</t>
-  </si>
-  <si>
-    <t>792</t>
-  </si>
-  <si>
-    <t>794</t>
-  </si>
-  <si>
-    <t>795</t>
-  </si>
-  <si>
-    <t>796</t>
-  </si>
-  <si>
-    <t>797</t>
-  </si>
-  <si>
-    <t>798</t>
-  </si>
-  <si>
-    <t>799</t>
-  </si>
-  <si>
-    <t>VITALLIS DIAGNOSTICA</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>VITALLIS DIAGNOSTICA LTDA</t>
-  </si>
-  <si>
-    <t>01.663.156/0001-15</t>
-  </si>
-  <si>
-    <t>801</t>
-  </si>
-  <si>
-    <t>J R BASTOS</t>
-  </si>
-  <si>
-    <t>803</t>
-  </si>
-  <si>
-    <t>14 %</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>68 %</t>
-  </si>
-  <si>
-    <t>805</t>
-  </si>
-  <si>
-    <t>806</t>
-  </si>
-  <si>
-    <t>807</t>
-  </si>
-  <si>
-    <t>808</t>
-  </si>
-  <si>
-    <t>809</t>
-  </si>
-  <si>
-    <t>810</t>
-  </si>
-  <si>
-    <t>811</t>
-  </si>
-  <si>
-    <t>812</t>
-  </si>
-  <si>
-    <t>813</t>
-  </si>
-  <si>
-    <t>814</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO</t>
-  </si>
-  <si>
-    <t>815</t>
-  </si>
-  <si>
-    <t>816</t>
-  </si>
-  <si>
-    <t>817</t>
-  </si>
-  <si>
-    <t>818</t>
-  </si>
-  <si>
-    <t>CAMEDIC</t>
-  </si>
-  <si>
-    <t>819</t>
-  </si>
-  <si>
-    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRELI</t>
-  </si>
-  <si>
-    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
-  </si>
-  <si>
-    <t>28.450.020/0001-83</t>
-  </si>
-  <si>
-    <t>E.R.M COMERCIO</t>
-  </si>
-  <si>
-    <t>820</t>
-  </si>
-  <si>
-    <t>E.R.M COMERCIO E SERVICOS</t>
-  </si>
-  <si>
-    <t>E. R. M. DE SOUZA LTDA</t>
-  </si>
-  <si>
-    <t>31.597.128/0001-08</t>
-  </si>
-  <si>
-    <t>821</t>
-  </si>
-  <si>
-    <t>MEDLIFE PRODUTOS</t>
-  </si>
-  <si>
-    <t>822</t>
-  </si>
-  <si>
-    <t>MEDLIFE PRODUTOS MEDICO-HOSPITALARES</t>
-  </si>
-  <si>
-    <t>MEDLIFE PRODUTOS MEDICO-HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>45.772.861/0001-26</t>
-  </si>
-  <si>
-    <t>823</t>
-  </si>
-  <si>
-    <t>826</t>
-  </si>
-  <si>
-    <t>827</t>
-  </si>
-  <si>
-    <t>MAIS MED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>829</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
-    <t>832</t>
-  </si>
-  <si>
-    <t>833</t>
-  </si>
-  <si>
-    <t>834</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>836</t>
-  </si>
-  <si>
-    <t>837</t>
-  </si>
-  <si>
-    <t>838</t>
-  </si>
-  <si>
-    <t>839</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>841</t>
-  </si>
-  <si>
-    <t>842</t>
-  </si>
-  <si>
-    <t>843</t>
-  </si>
-  <si>
-    <t>844</t>
-  </si>
-  <si>
-    <t>MERCANTE HOSPITALAR</t>
-  </si>
-  <si>
-    <t>852</t>
-  </si>
-  <si>
-    <t>MERCANTE DISTRIBUIDOR HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>51.793.632/0001-90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">andrey    </t>
-  </si>
-  <si>
-    <t>853</t>
-  </si>
-  <si>
-    <t>856</t>
-  </si>
-  <si>
-    <t>859</t>
-  </si>
-  <si>
-    <t>COMPRATES COMERCIAL</t>
-  </si>
-  <si>
-    <t>861</t>
-  </si>
-  <si>
-    <t>COMPRATES COMERCIAL FARMACEUTICA E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>COMPRATES COMERCIAL FARMACEUTICA E HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>96.845.896/0001-89</t>
-  </si>
-  <si>
-    <t>864</t>
-  </si>
-  <si>
-    <t>865</t>
-  </si>
-  <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>867</t>
-  </si>
-  <si>
-    <t>868</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSP.</t>
-  </si>
-  <si>
-    <t>869</t>
-  </si>
-  <si>
-    <t>CIDALAB COMERCIO</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>FARMAGUEDES COMERCIO</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>D &amp; V COMERCIO</t>
-  </si>
-  <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>D &amp; V COMERCIO DE MATERIAL HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>05.964.983/0001-08</t>
-  </si>
-  <si>
-    <t>V L R LIMA</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>J.J DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>876</t>
-  </si>
-  <si>
-    <t>J.J DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>07.187.827/0001-03</t>
-  </si>
-  <si>
-    <t>877</t>
-  </si>
-  <si>
-    <t>878</t>
-  </si>
-  <si>
-    <t>BIOMED MATERIAIS</t>
-  </si>
-  <si>
-    <t>879</t>
-  </si>
-  <si>
-    <t>59 %</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>881</t>
-  </si>
-  <si>
-    <t>44 %</t>
-  </si>
-  <si>
-    <t>884</t>
-  </si>
-  <si>
-    <t>MEDFASP SERVICOS &amp; COMERCIO</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>90 %</t>
-  </si>
-  <si>
-    <t>R5 SOLUCOES</t>
-  </si>
-  <si>
-    <t>886</t>
-  </si>
-  <si>
-    <t>86 %</t>
-  </si>
-  <si>
-    <t>887</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
-    <t>890</t>
-  </si>
-  <si>
-    <t>F R HOSPITALAR MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>891</t>
-  </si>
-  <si>
-    <t>892</t>
-  </si>
-  <si>
-    <t>893</t>
-  </si>
-  <si>
-    <t>DL MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>894</t>
-  </si>
-  <si>
-    <t>DL MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>48.058.173/0001-97</t>
-  </si>
-  <si>
-    <t>A INICIAR</t>
-  </si>
-  <si>
-    <t>895</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>4M BR COMERCIO</t>
-  </si>
-  <si>
-    <t>897</t>
-  </si>
-  <si>
-    <t>898</t>
-  </si>
-  <si>
-    <t>52 %</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>902</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO</t>
-  </si>
-  <si>
-    <t>903</t>
-  </si>
-  <si>
-    <t>97 %</t>
-  </si>
-  <si>
-    <t>904</t>
-  </si>
-  <si>
-    <t>905</t>
-  </si>
-  <si>
-    <t>PLENA DISTRIBUIDORA RN</t>
-  </si>
-  <si>
-    <t>906</t>
-  </si>
-  <si>
-    <t>907</t>
-  </si>
-  <si>
-    <t>908</t>
-  </si>
-  <si>
-    <t>909</t>
-  </si>
-  <si>
-    <t>910</t>
-  </si>
-  <si>
-    <t>PROMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>911</t>
-  </si>
-  <si>
-    <t>912</t>
-  </si>
-  <si>
-    <t>46 %</t>
-  </si>
-  <si>
-    <t>913</t>
-  </si>
-  <si>
-    <t>914</t>
-  </si>
-  <si>
-    <t>915</t>
-  </si>
-  <si>
-    <t>916</t>
-  </si>
-  <si>
-    <t>917</t>
-  </si>
-  <si>
-    <t>918</t>
-  </si>
-  <si>
-    <t>919</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>921</t>
-  </si>
-  <si>
-    <t>LOPES BARRETO</t>
-  </si>
-  <si>
-    <t>922</t>
-  </si>
-  <si>
-    <t>923</t>
-  </si>
-  <si>
-    <t>DIST. RIO PARNAIBA</t>
-  </si>
-  <si>
-    <t>925</t>
-  </si>
-  <si>
-    <t>D. ARAUJO</t>
-  </si>
-  <si>
-    <t>926</t>
-  </si>
-  <si>
-    <t>927</t>
-  </si>
-  <si>
-    <t>ENDOMED COMERCIO</t>
-  </si>
-  <si>
-    <t>928</t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>HOSP CENTER</t>
-  </si>
-  <si>
-    <t>931</t>
-  </si>
-  <si>
-    <t>HOSP CENTER COMERCIO DE PRODUTOS ODONTO-MEDICO-HOS</t>
-  </si>
-  <si>
-    <t>16.642.091/0001-07</t>
-  </si>
-  <si>
-    <t>932</t>
-  </si>
-  <si>
-    <t>933</t>
-  </si>
-  <si>
-    <t>934</t>
-  </si>
-  <si>
-    <t>935</t>
-  </si>
-  <si>
-    <t>MERCOSUL DIST.</t>
-  </si>
-  <si>
-    <t>936</t>
-  </si>
-  <si>
-    <t>MERCOSUL DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>MERCOSUL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>28.973.504/0001-07</t>
-  </si>
-  <si>
-    <t>937</t>
-  </si>
-  <si>
-    <t>938</t>
-  </si>
-  <si>
-    <t>939</t>
-  </si>
-  <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>941</t>
-  </si>
-  <si>
-    <t>942</t>
-  </si>
-  <si>
-    <t>943</t>
-  </si>
-  <si>
-    <t>RF PRODUTOS HOSPITALARES</t>
-  </si>
-  <si>
-    <t>944</t>
-  </si>
-  <si>
-    <t>945</t>
-  </si>
-  <si>
-    <t>VAL MED PRODUTOS E EQUIP.</t>
-  </si>
-  <si>
-    <t>946</t>
-  </si>
-  <si>
-    <t>947</t>
-  </si>
-  <si>
-    <t>948</t>
-  </si>
-  <si>
-    <t>949</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>D. ARAUJO COMERCIO</t>
-  </si>
-  <si>
-    <t>951</t>
-  </si>
-  <si>
-    <t>953</t>
-  </si>
-  <si>
-    <t>MERCANTE DISTRIBUIDOR HOSP.</t>
-  </si>
-  <si>
-    <t>954</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL</t>
-  </si>
-  <si>
-    <t>955</t>
-  </si>
-  <si>
-    <t>956</t>
-  </si>
-  <si>
-    <t>BANDEIRANTES LAB</t>
-  </si>
-  <si>
-    <t>957</t>
-  </si>
-  <si>
-    <t>LABAND</t>
-  </si>
-  <si>
-    <t>BANDEIRANTES LAB PROD FARMACEUTICOS E HOSPITALARES</t>
-  </si>
-  <si>
-    <t>70.027.479/0001-35</t>
-  </si>
-  <si>
-    <t>958</t>
-  </si>
-  <si>
-    <t>959</t>
-  </si>
-  <si>
-    <t>70 %</t>
-  </si>
-  <si>
-    <t>JFB DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSP</t>
-  </si>
-  <si>
-    <t>963</t>
-  </si>
-  <si>
-    <t>964</t>
-  </si>
-  <si>
-    <t>965</t>
-  </si>
-  <si>
-    <t>966</t>
-  </si>
-  <si>
-    <t>967</t>
-  </si>
-  <si>
-    <t>968</t>
-  </si>
-  <si>
-    <t>HOSPMED - PIAUI</t>
-  </si>
-  <si>
-    <t>969</t>
-  </si>
-  <si>
-    <t>HOSPMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>HOSPMED LTDA</t>
-  </si>
-  <si>
-    <t>00.156.820/0001-77</t>
-  </si>
-  <si>
-    <t>60 %</t>
-  </si>
-  <si>
-    <t>970</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>972</t>
-  </si>
-  <si>
-    <t>82 %</t>
-  </si>
-  <si>
-    <t>973</t>
-  </si>
-  <si>
-    <t>974</t>
-  </si>
-  <si>
-    <t>UNI-RIM UNIDADE</t>
-  </si>
-  <si>
-    <t>975</t>
-  </si>
-  <si>
-    <t>UNI-RIM UNIDADE DE DOENCAS RENAIS</t>
-  </si>
-  <si>
-    <t>MARCELO BARBOSA LEITE</t>
-  </si>
-  <si>
-    <t>02.553.837/0001-93</t>
-  </si>
-  <si>
-    <t>ULTRA TEXTIL</t>
-  </si>
-  <si>
-    <t>976</t>
-  </si>
-  <si>
-    <t>ALYNE FARMA</t>
-  </si>
-  <si>
-    <t>977</t>
-  </si>
-  <si>
-    <t>FARMACIAS CLARA POPULAR</t>
-  </si>
-  <si>
-    <t>ALYNE FARMA LTDA</t>
-  </si>
-  <si>
-    <t>14.674.114/0001-21</t>
-  </si>
-  <si>
-    <t>978</t>
-  </si>
-  <si>
-    <t>979</t>
-  </si>
-  <si>
-    <t>980</t>
-  </si>
-  <si>
-    <t>981</t>
-  </si>
-  <si>
-    <t>982</t>
-  </si>
-  <si>
-    <t>MED &amp; FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>983</t>
-  </si>
-  <si>
-    <t>J LAERCIO</t>
-  </si>
-  <si>
-    <t>984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabio     </t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>986</t>
-  </si>
-  <si>
-    <t>47 %</t>
-  </si>
-  <si>
-    <t>987</t>
-  </si>
-  <si>
-    <t>989</t>
-  </si>
-  <si>
-    <t>89 %</t>
-  </si>
-  <si>
-    <t>EXPRESS DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>991</t>
-  </si>
-  <si>
-    <t>992</t>
-  </si>
-  <si>
-    <t>996</t>
-  </si>
-  <si>
-    <t>77 %</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>85 %</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>T S DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>43 %</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>53 %</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>PB MED</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>39 %</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>14.416.886/0001-63</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>GM FARMA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>81 %</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>C G FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1030</t>
-  </si>
-  <si>
-    <t>ALTAMED</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>21.581.445/0001-82</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO</t>
-  </si>
-  <si>
-    <t>Região03</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>FERMATA</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>66.175.139/0001-84</t>
-  </si>
-  <si>
-    <t>RC HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>26.147.597/0001-95</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>05.003.408/0001-30</t>
-  </si>
-  <si>
-    <t>PLENA DIST - RN</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>PLENA DIST - PE</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>1049</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>CIRURGICA SHALOM</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>MP COMERCIO</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>38 %</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>MONTEBELLO</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>08.674.752/0001-40</t>
-  </si>
-  <si>
-    <t>84 %</t>
-  </si>
-  <si>
-    <t>1062</t>
-  </si>
-  <si>
-    <t>D FARIAS LIMA</t>
-  </si>
-  <si>
-    <t>1063</t>
-  </si>
-  <si>
-    <t>EXPRESS DIST.</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>1066</t>
-  </si>
-  <si>
-    <t>83 %</t>
-  </si>
-  <si>
-    <t>1067</t>
-  </si>
-  <si>
-    <t>1068</t>
-  </si>
-  <si>
-    <t>LS MATERIAIS (HELDER WALNER)</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>A M FARMA - MA</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>A M FARMA - PI</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL MEDICO</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>64.190.875/0001-86</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>39.324.410/0001-23</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>36 %</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>35 %</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1083</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>32.658.023/0001-84</t>
-  </si>
-  <si>
-    <t>13 %</t>
-  </si>
-  <si>
-    <t>CONQUISTA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>12.418.191/0001-95</t>
-  </si>
-  <si>
-    <t>30 %</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>F MELO</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>C J A PARENTE</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>83.646.307/0001-91</t>
-  </si>
-  <si>
-    <t>NORTE GREEN</t>
-  </si>
-  <si>
-    <t>1091</t>
-  </si>
-  <si>
-    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
-  </si>
-  <si>
-    <t>24.218.223/0001-98</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>1093</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>46.359.681/0001-80</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>1096</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL</t>
-  </si>
-  <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>64 %</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>61 %</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA DE MED.</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
     <t>1108</t>
   </si>
   <si>
@@ -5533,6 +5536,9 @@
   </si>
   <si>
     <t>20.001.049/0001-76</t>
+  </si>
+  <si>
+    <t>12 %</t>
   </si>
   <si>
     <t>1111</t>
@@ -37128,7 +37134,7 @@
       </c>
       <c r="C561" s="9"/>
       <c r="D561" s="9" t="s">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="E561" s="8" t="s">
         <v>1314</v>
@@ -37169,7 +37175,7 @@
         <v>242444.07</v>
       </c>
       <c r="S561" s="12" t="n">
-        <v>190038.42</v>
+        <v>181247.22</v>
       </c>
       <c r="T561" s="9" t="s">
         <v>30</v>
@@ -40417,7 +40423,7 @@
         <v>48121.96</v>
       </c>
       <c r="S619" s="12" t="n">
-        <v>32909.44</v>
+        <v>35072.44</v>
       </c>
       <c r="T619" s="9" t="s">
         <v>30</v>
@@ -54458,7 +54464,7 @@
       <c r="L870" s="5"/>
       <c r="M870" s="5"/>
       <c r="N870" s="4" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O870" s="6" t="n">
         <v>46233.658307292</v>
@@ -54939,13 +54945,13 @@
         <v>21</v>
       </c>
       <c r="E879" s="8" t="s">
-        <v>1314</v>
+        <v>1834</v>
       </c>
       <c r="F879" s="9" t="s">
         <v>1472</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -54998,22 +55004,22 @@
         <v>282</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -55051,13 +55057,13 @@
         <v>21</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>282</v>
+        <v>1841</v>
       </c>
       <c r="F881" s="9" t="s">
         <v>273</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -55089,7 +55095,7 @@
         <v>73636</v>
       </c>
       <c r="S881" s="12" t="n">
-        <v>0</v>
+        <v>8980</v>
       </c>
       <c r="T881" s="9" t="s">
         <v>30</v>
@@ -55119,7 +55125,7 @@
         <v>55630246.5126</v>
       </c>
       <c r="S882" s="15" t="n">
-        <v>53671867.705</v>
+        <v>53674219.505</v>
       </c>
       <c r="T882" s="16"/>
     </row>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1847">
   <si>
     <t>ID</t>
   </si>
@@ -3957,7 +3957,7 @@
     <t>04.112.864/0001-56</t>
   </si>
   <si>
-    <t>75 %</t>
+    <t>78 %</t>
   </si>
   <si>
     <t>724</t>
@@ -4983,9 +4983,6 @@
     <t>997</t>
   </si>
   <si>
-    <t>85 %</t>
-  </si>
-  <si>
     <t>998</t>
   </si>
   <si>
@@ -5094,7 +5091,7 @@
     <t>1027</t>
   </si>
   <si>
-    <t>81 %</t>
+    <t>98 %</t>
   </si>
   <si>
     <t>1028</t>
@@ -5121,7 +5118,7 @@
     <t>21.581.445/0001-82</t>
   </si>
   <si>
-    <t>ALINE CERBINO</t>
+    <t>ALINE CERBINO - PA</t>
   </si>
   <si>
     <t>Região03</t>
@@ -5265,9 +5262,6 @@
     <t>08.674.752/0001-40</t>
   </si>
   <si>
-    <t>84 %</t>
-  </si>
-  <si>
     <t>1062</t>
   </si>
   <si>
@@ -5364,7 +5358,7 @@
     <t>1079</t>
   </si>
   <si>
-    <t>35 %</t>
+    <t>34 %</t>
   </si>
   <si>
     <t>1080</t>
@@ -5487,9 +5481,6 @@
     <t>1100</t>
   </si>
   <si>
-    <t>64 %</t>
-  </si>
-  <si>
     <t>1101</t>
   </si>
   <si>
@@ -5499,6 +5490,9 @@
     <t>1102</t>
   </si>
   <si>
+    <t>57 %</t>
+  </si>
+  <si>
     <t>1103</t>
   </si>
   <si>
@@ -5517,9 +5511,6 @@
     <t>1107</t>
   </si>
   <si>
-    <t>78 %</t>
-  </si>
-  <si>
     <t>1108</t>
   </si>
   <si>
@@ -5542,6 +5533,27 @@
   </si>
   <si>
     <t>1111</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>1118</t>
   </si>
 </sst>
 </file>
@@ -5735,7 +5747,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:T882"/>
+  <dimension ref="A1:T889"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -37134,7 +37146,7 @@
       </c>
       <c r="C561" s="9"/>
       <c r="D561" s="9" t="s">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="E561" s="8" t="s">
         <v>1314</v>
@@ -37175,7 +37187,7 @@
         <v>242444.07</v>
       </c>
       <c r="S561" s="12" t="n">
-        <v>181247.22</v>
+        <v>190038.42</v>
       </c>
       <c r="T561" s="9" t="s">
         <v>30</v>
@@ -44944,7 +44956,7 @@
       <c r="L700" s="5"/>
       <c r="M700" s="5"/>
       <c r="N700" s="4" t="s">
-        <v>1285</v>
+        <v>27</v>
       </c>
       <c r="O700" s="6" t="n">
         <v>46170.326156447</v>
@@ -49345,13 +49357,13 @@
         <v>21</v>
       </c>
       <c r="E779" s="8" t="s">
-        <v>1656</v>
+        <v>22</v>
       </c>
       <c r="F779" s="9" t="s">
         <v>942</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -49368,7 +49380,7 @@
       <c r="L779" s="10"/>
       <c r="M779" s="10"/>
       <c r="N779" s="9" t="s">
-        <v>1285</v>
+        <v>27</v>
       </c>
       <c r="O779" s="11" t="n">
         <v>46202.331869711</v>
@@ -49383,7 +49395,7 @@
         <v>43841.84</v>
       </c>
       <c r="S779" s="12" t="n">
-        <v>37195.2</v>
+        <v>43841.84</v>
       </c>
       <c r="T779" s="9" t="s">
         <v>30</v>
@@ -49407,7 +49419,7 @@
         <v>1458</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
@@ -49460,10 +49472,10 @@
         <v>22</v>
       </c>
       <c r="F781" s="9" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G781" s="9" t="s">
         <v>1659</v>
-      </c>
-      <c r="G781" s="9" t="s">
-        <v>1660</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -49519,7 +49531,7 @@
         <v>188</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -49569,13 +49581,13 @@
         <v>21</v>
       </c>
       <c r="E783" s="8" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F783" s="9" t="s">
         <v>1662</v>
       </c>
-      <c r="F783" s="9" t="s">
+      <c r="G783" s="9" t="s">
         <v>1663</v>
-      </c>
-      <c r="G783" s="9" t="s">
-        <v>1664</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -49631,7 +49643,7 @@
         <v>121</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -49687,7 +49699,7 @@
         <v>72</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -49743,7 +49755,7 @@
         <v>329</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -49799,7 +49811,7 @@
         <v>1472</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -49855,7 +49867,7 @@
         <v>246</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -49911,7 +49923,7 @@
         <v>1099</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -49961,13 +49973,13 @@
         <v>21</v>
       </c>
       <c r="E790" s="3" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F790" s="4" t="s">
         <v>292</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -50023,7 +50035,7 @@
         <v>259</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -50079,7 +50091,7 @@
         <v>55</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -50135,7 +50147,7 @@
         <v>1096</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -50191,7 +50203,7 @@
         <v>1520</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -50244,10 +50256,10 @@
         <v>22</v>
       </c>
       <c r="F795" s="9" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G795" s="9" t="s">
         <v>1677</v>
-      </c>
-      <c r="G795" s="9" t="s">
-        <v>1678</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -50303,7 +50315,7 @@
         <v>354</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -50359,7 +50371,7 @@
         <v>952</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -50409,13 +50421,13 @@
         <v>21</v>
       </c>
       <c r="E798" s="3" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>1295</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -50471,7 +50483,7 @@
         <v>1621</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
@@ -50524,22 +50536,22 @@
         <v>22</v>
       </c>
       <c r="F800" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G800" s="4" t="s">
         <v>1684</v>
-      </c>
-      <c r="G800" s="4" t="s">
-        <v>1685</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="J800" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="K800" s="4" t="s">
         <v>1686</v>
-      </c>
-      <c r="J800" s="4" t="s">
-        <v>1686</v>
-      </c>
-      <c r="K800" s="4" t="s">
-        <v>1687</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -50583,7 +50595,7 @@
         <v>1426</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
@@ -50636,10 +50648,10 @@
         <v>22</v>
       </c>
       <c r="F802" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G802" s="4" t="s">
         <v>1689</v>
-      </c>
-      <c r="G802" s="4" t="s">
-        <v>1690</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -50695,7 +50707,7 @@
         <v>1575</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -50751,7 +50763,7 @@
         <v>363</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -50801,13 +50813,13 @@
         <v>21</v>
       </c>
       <c r="E805" s="8" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="F805" s="9" t="s">
         <v>826</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -50839,7 +50851,7 @@
         <v>48354.5496</v>
       </c>
       <c r="S805" s="12" t="n">
-        <v>39078.132</v>
+        <v>47286.5976</v>
       </c>
       <c r="T805" s="9" t="s">
         <v>30</v>
@@ -50860,10 +50872,10 @@
         <v>22</v>
       </c>
       <c r="F806" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G806" s="4" t="s">
         <v>1695</v>
-      </c>
-      <c r="G806" s="4" t="s">
-        <v>1696</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -50916,22 +50928,22 @@
         <v>1654</v>
       </c>
       <c r="F807" s="9" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G807" s="9" t="s">
         <v>1697</v>
-      </c>
-      <c r="G807" s="9" t="s">
-        <v>1698</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
+        <v>1698</v>
+      </c>
+      <c r="J807" s="9" t="s">
         <v>1699</v>
       </c>
-      <c r="J807" s="9" t="s">
+      <c r="K807" s="9" t="s">
         <v>1700</v>
-      </c>
-      <c r="K807" s="9" t="s">
-        <v>1701</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
@@ -50945,7 +50957,7 @@
         <v>1454</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
@@ -50954,7 +50966,7 @@
         <v>44782.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="808" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -50975,7 +50987,7 @@
         <v>1520</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -51028,22 +51040,22 @@
         <v>22</v>
       </c>
       <c r="F809" s="9" t="s">
+        <v>1704</v>
+      </c>
+      <c r="G809" s="9" t="s">
         <v>1705</v>
-      </c>
-      <c r="G809" s="9" t="s">
-        <v>1706</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J809" s="9" t="s">
+        <v>1706</v>
+      </c>
+      <c r="K809" s="9" t="s">
         <v>1707</v>
-      </c>
-      <c r="K809" s="9" t="s">
-        <v>1708</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -51057,7 +51069,7 @@
         <v>1454</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -51066,7 +51078,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="810" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -51084,22 +51096,22 @@
         <v>22</v>
       </c>
       <c r="F810" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G810" s="4" t="s">
         <v>1709</v>
-      </c>
-      <c r="G810" s="4" t="s">
-        <v>1710</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J810" s="4" t="s">
         <v>1711</v>
       </c>
-      <c r="J810" s="4" t="s">
+      <c r="K810" s="4" t="s">
         <v>1712</v>
-      </c>
-      <c r="K810" s="4" t="s">
-        <v>1713</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -51113,7 +51125,7 @@
         <v>1454</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -51122,7 +51134,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="811" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -51140,22 +51152,22 @@
         <v>22</v>
       </c>
       <c r="F811" s="9" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G811" s="9" t="s">
         <v>1714</v>
-      </c>
-      <c r="G811" s="9" t="s">
-        <v>1715</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
+        <v>1715</v>
+      </c>
+      <c r="J811" s="9" t="s">
         <v>1716</v>
       </c>
-      <c r="J811" s="9" t="s">
+      <c r="K811" s="9" t="s">
         <v>1717</v>
-      </c>
-      <c r="K811" s="9" t="s">
-        <v>1718</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -51169,7 +51181,7 @@
         <v>1454</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -51178,7 +51190,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="812" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -51196,10 +51208,10 @@
         <v>22</v>
       </c>
       <c r="F812" s="4" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G812" s="4" t="s">
         <v>1719</v>
-      </c>
-      <c r="G812" s="4" t="s">
-        <v>1720</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -51252,10 +51264,10 @@
         <v>22</v>
       </c>
       <c r="F813" s="9" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G813" s="9" t="s">
         <v>1721</v>
-      </c>
-      <c r="G813" s="9" t="s">
-        <v>1722</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -51311,7 +51323,7 @@
         <v>325</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -51367,7 +51379,7 @@
         <v>72</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -51423,7 +51435,7 @@
         <v>386</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -51479,7 +51491,7 @@
         <v>246</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -51535,7 +51547,7 @@
         <v>1552</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -51591,7 +51603,7 @@
         <v>1410</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -51647,7 +51659,7 @@
         <v>161</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -51703,7 +51715,7 @@
         <v>1487</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -51759,7 +51771,7 @@
         <v>1552</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -51815,7 +51827,7 @@
         <v>1371</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -51871,7 +51883,7 @@
         <v>1649</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -51924,10 +51936,10 @@
         <v>22</v>
       </c>
       <c r="F825" s="9" t="s">
+        <v>1733</v>
+      </c>
+      <c r="G825" s="9" t="s">
         <v>1734</v>
-      </c>
-      <c r="G825" s="9" t="s">
-        <v>1735</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -51983,7 +51995,7 @@
         <v>1470</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -52039,7 +52051,7 @@
         <v>329</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -52092,10 +52104,10 @@
         <v>22</v>
       </c>
       <c r="F828" s="4" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G828" s="4" t="s">
         <v>1738</v>
-      </c>
-      <c r="G828" s="4" t="s">
-        <v>1739</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -52151,7 +52163,7 @@
         <v>481</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -52201,13 +52213,13 @@
         <v>21</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -52263,7 +52275,7 @@
         <v>307</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -52319,7 +52331,7 @@
         <v>966</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -52372,22 +52384,22 @@
         <v>22</v>
       </c>
       <c r="F833" s="9" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G833" s="9" t="s">
         <v>1745</v>
-      </c>
-      <c r="G833" s="9" t="s">
-        <v>1746</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
+        <v>1746</v>
+      </c>
+      <c r="J833" s="9" t="s">
         <v>1747</v>
       </c>
-      <c r="J833" s="9" t="s">
+      <c r="K833" s="9" t="s">
         <v>1748</v>
-      </c>
-      <c r="K833" s="9" t="s">
-        <v>1749</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -52425,13 +52437,13 @@
         <v>21</v>
       </c>
       <c r="E834" s="3" t="s">
-        <v>1750</v>
+        <v>22</v>
       </c>
       <c r="F834" s="4" t="s">
         <v>1326</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
@@ -52448,7 +52460,7 @@
       <c r="L834" s="5"/>
       <c r="M834" s="5"/>
       <c r="N834" s="4" t="s">
-        <v>1285</v>
+        <v>27</v>
       </c>
       <c r="O834" s="6" t="n">
         <v>46224.377425313</v>
@@ -52463,7 +52475,7 @@
         <v>14020</v>
       </c>
       <c r="S834" s="7" t="n">
-        <v>11776.8</v>
+        <v>14020</v>
       </c>
       <c r="T834" s="4" t="s">
         <v>30</v>
@@ -52484,10 +52496,10 @@
         <v>22</v>
       </c>
       <c r="F835" s="9" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="G835" s="9" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -52540,10 +52552,10 @@
         <v>22</v>
       </c>
       <c r="F836" s="4" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="G836" s="4" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -52599,7 +52611,7 @@
         <v>1600</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -52655,7 +52667,7 @@
         <v>1261</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -52705,13 +52717,13 @@
         <v>21</v>
       </c>
       <c r="E839" s="8" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="F839" s="9" t="s">
         <v>200</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -52761,13 +52773,13 @@
         <v>21</v>
       </c>
       <c r="E840" s="3" t="s">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="F840" s="4" t="s">
         <v>307</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -52784,7 +52796,7 @@
       <c r="L840" s="5"/>
       <c r="M840" s="5"/>
       <c r="N840" s="4" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O840" s="6" t="n">
         <v>46226.339257789</v>
@@ -52799,7 +52811,7 @@
         <v>4847.04</v>
       </c>
       <c r="S840" s="7" t="n">
-        <v>0</v>
+        <v>4847.04</v>
       </c>
       <c r="T840" s="4" t="s">
         <v>30</v>
@@ -52820,10 +52832,10 @@
         <v>282</v>
       </c>
       <c r="F841" s="9" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G841" s="9" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -52876,10 +52888,10 @@
         <v>22</v>
       </c>
       <c r="F842" s="4" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="G842" s="4" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -52932,10 +52944,10 @@
         <v>22</v>
       </c>
       <c r="F843" s="9" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="G843" s="9" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -52988,10 +53000,10 @@
         <v>282</v>
       </c>
       <c r="F844" s="4" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="G844" s="4" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -53044,27 +53056,27 @@
         <v>22</v>
       </c>
       <c r="F845" s="9" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="G845" s="9" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
+        <v>1767</v>
+      </c>
+      <c r="J845" s="9" t="s">
         <v>1769</v>
       </c>
-      <c r="J845" s="9" t="s">
-        <v>1771</v>
-      </c>
       <c r="K845" s="9" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
       <c r="N845" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O845" s="11" t="n">
         <v>46226.658852465</v>
@@ -53100,22 +53112,22 @@
         <v>22</v>
       </c>
       <c r="F846" s="4" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="G846" s="4" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -53159,7 +53171,7 @@
         <v>589</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -53215,7 +53227,7 @@
         <v>1176</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -53271,7 +53283,7 @@
         <v>620</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -53327,7 +53339,7 @@
         <v>307</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -53377,13 +53389,13 @@
         <v>21</v>
       </c>
       <c r="E851" s="8" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="F851" s="9" t="s">
         <v>1600</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -53433,13 +53445,13 @@
         <v>21</v>
       </c>
       <c r="E852" s="3" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="F852" s="4" t="s">
         <v>578</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -53468,7 +53480,7 @@
         <v>29</v>
       </c>
       <c r="R852" s="7" t="n">
-        <v>21909.9</v>
+        <v>22175.52</v>
       </c>
       <c r="S852" s="7" t="n">
         <v>7580.4</v>
@@ -53495,7 +53507,7 @@
         <v>1520</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -53512,7 +53524,7 @@
       <c r="L853" s="10"/>
       <c r="M853" s="10"/>
       <c r="N853" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O853" s="11" t="n">
         <v>46230.663143785</v>
@@ -53548,22 +53560,22 @@
         <v>22</v>
       </c>
       <c r="F854" s="4" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="G854" s="4" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="J854" s="4" t="s">
         <v>1786</v>
       </c>
-      <c r="J854" s="4" t="s">
-        <v>1788</v>
-      </c>
       <c r="K854" s="4" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -53601,25 +53613,25 @@
         <v>21</v>
       </c>
       <c r="E855" s="8" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F855" s="9" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G855" s="9" t="s">
         <v>1790</v>
-      </c>
-      <c r="F855" s="9" t="s">
-        <v>1791</v>
-      </c>
-      <c r="G855" s="9" t="s">
-        <v>1792</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
+        <v>1789</v>
+      </c>
+      <c r="J855" s="9" t="s">
         <v>1791</v>
       </c>
-      <c r="J855" s="9" t="s">
-        <v>1793</v>
-      </c>
       <c r="K855" s="9" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
@@ -53657,13 +53669,13 @@
         <v>21</v>
       </c>
       <c r="E856" s="3" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="F856" s="4" t="s">
         <v>273</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -53719,7 +53731,7 @@
         <v>1277</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -53775,7 +53787,7 @@
         <v>589</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -53792,7 +53804,7 @@
       <c r="L858" s="5"/>
       <c r="M858" s="5"/>
       <c r="N858" s="4" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O858" s="6" t="n">
         <v>46232.379035069</v>
@@ -53831,7 +53843,7 @@
         <v>1261</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -53884,10 +53896,10 @@
         <v>282</v>
       </c>
       <c r="F860" s="4" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="G860" s="4" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -53940,22 +53952,22 @@
         <v>282</v>
       </c>
       <c r="F861" s="9" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="G861" s="9" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1802</v>
+      </c>
+      <c r="J861" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K861" s="9" t="s">
         <v>1804</v>
-      </c>
-      <c r="J861" s="9" t="s">
-        <v>1805</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1806</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -53969,7 +53981,7 @@
         <v>1454</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>39463.12</v>
@@ -53978,7 +53990,7 @@
         <v>0</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="862" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -53996,22 +54008,22 @@
         <v>22</v>
       </c>
       <c r="F862" s="4" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
+        <v>1805</v>
+      </c>
+      <c r="J862" s="4" t="s">
         <v>1807</v>
       </c>
-      <c r="J862" s="4" t="s">
-        <v>1809</v>
-      </c>
       <c r="K862" s="4" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -54055,7 +54067,7 @@
         <v>856</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -54111,7 +54123,7 @@
         <v>259</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -54164,22 +54176,22 @@
         <v>22</v>
       </c>
       <c r="F865" s="9" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="G865" s="9" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="J865" s="9" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="K865" s="9" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -54223,7 +54235,7 @@
         <v>487</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -54279,7 +54291,7 @@
         <v>518</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -54296,7 +54308,7 @@
       <c r="L867" s="10"/>
       <c r="M867" s="10"/>
       <c r="N867" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O867" s="11" t="n">
         <v>46233.652091435</v>
@@ -54335,7 +54347,7 @@
         <v>1552</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -54391,7 +54403,7 @@
         <v>1130</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -54408,7 +54420,7 @@
       <c r="L869" s="10"/>
       <c r="M869" s="10"/>
       <c r="N869" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O869" s="11" t="n">
         <v>46233.656732905</v>
@@ -54444,10 +54456,10 @@
         <v>22</v>
       </c>
       <c r="F870" s="4" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -54503,7 +54515,7 @@
         <v>352</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -54520,7 +54532,7 @@
       <c r="L871" s="10"/>
       <c r="M871" s="10"/>
       <c r="N871" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O871" s="11" t="n">
         <v>46233.660123229</v>
@@ -54553,13 +54565,13 @@
         <v>21</v>
       </c>
       <c r="E872" s="3" t="s">
-        <v>1824</v>
+        <v>22</v>
       </c>
       <c r="F872" s="4" t="s">
         <v>348</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -54591,7 +54603,7 @@
         <v>31208</v>
       </c>
       <c r="S872" s="7" t="n">
-        <v>20008</v>
+        <v>31208</v>
       </c>
       <c r="T872" s="4" t="s">
         <v>30</v>
@@ -54609,13 +54621,13 @@
         <v>21</v>
       </c>
       <c r="E873" s="8" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="F873" s="9" t="s">
         <v>942</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -54665,13 +54677,13 @@
         <v>21</v>
       </c>
       <c r="E874" s="3" t="s">
-        <v>1492</v>
+        <v>1825</v>
       </c>
       <c r="F874" s="4" t="s">
         <v>259</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -54688,7 +54700,7 @@
       <c r="L874" s="5"/>
       <c r="M874" s="5"/>
       <c r="N874" s="4" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="O874" s="6" t="n">
         <v>46233.666216817</v>
@@ -54703,7 +54715,7 @@
         <v>43189.08</v>
       </c>
       <c r="S874" s="7" t="n">
-        <v>19188</v>
+        <v>24462.72</v>
       </c>
       <c r="T874" s="4" t="s">
         <v>30</v>
@@ -54727,7 +54739,7 @@
         <v>1261</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -54780,10 +54792,10 @@
         <v>282</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="G876" s="4" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -54839,7 +54851,7 @@
         <v>72</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -54895,7 +54907,7 @@
         <v>405</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -54945,13 +54957,13 @@
         <v>21</v>
       </c>
       <c r="E879" s="8" t="s">
-        <v>1834</v>
+        <v>22</v>
       </c>
       <c r="F879" s="9" t="s">
         <v>1472</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -54968,7 +54980,7 @@
       <c r="L879" s="10"/>
       <c r="M879" s="10"/>
       <c r="N879" s="9" t="s">
-        <v>1511</v>
+        <v>27</v>
       </c>
       <c r="O879" s="11" t="n">
         <v>46233.677147419</v>
@@ -54983,7 +54995,7 @@
         <v>4083.2</v>
       </c>
       <c r="S879" s="12" t="n">
-        <v>3203.2</v>
+        <v>4083.2</v>
       </c>
       <c r="T879" s="9" t="s">
         <v>30</v>
@@ -55004,22 +55016,22 @@
         <v>282</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -55057,13 +55069,13 @@
         <v>21</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="F881" s="9" t="s">
         <v>273</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -55080,7 +55092,7 @@
       <c r="L881" s="10"/>
       <c r="M881" s="10"/>
       <c r="N881" s="9" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="O881" s="11" t="n">
         <v>46234.504198461</v>
@@ -55101,33 +55113,425 @@
         <v>30</v>
       </c>
     </row>
-    <row r="882" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A882" s="13" t="n">
-        <v>880</v>
-      </c>
-      <c r="B882" s="14"/>
-      <c r="C882" s="14"/>
-      <c r="D882" s="14"/>
-      <c r="E882" s="14"/>
-      <c r="F882" s="14"/>
-      <c r="G882" s="14"/>
-      <c r="H882" s="14"/>
-      <c r="I882" s="14"/>
-      <c r="J882" s="14"/>
-      <c r="K882" s="14"/>
-      <c r="L882" s="14"/>
-      <c r="M882" s="14"/>
-      <c r="N882" s="14"/>
-      <c r="O882" s="14"/>
-      <c r="P882" s="14"/>
-      <c r="Q882" s="14"/>
-      <c r="R882" s="15" t="n">
-        <v>55630246.5126</v>
-      </c>
-      <c r="S882" s="15" t="n">
-        <v>53674219.505</v>
-      </c>
-      <c r="T882" s="16"/>
+    <row r="882" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A882" s="3" t="n">
+        <v>951</v>
+      </c>
+      <c r="B882" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C882" s="4"/>
+      <c r="D882" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E882" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F882" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G882" s="4" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H882" s="5" t="n">
+        <v>46233</v>
+      </c>
+      <c r="I882" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="J882" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K882" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="L882" s="5"/>
+      <c r="M882" s="5"/>
+      <c r="N882" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O882" s="6" t="n">
+        <v>46237.439774109</v>
+      </c>
+      <c r="P882" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q882" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="R882" s="7" t="n">
+        <v>32661.36</v>
+      </c>
+      <c r="S882" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T882" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="883" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A883" s="8" t="n">
+        <v>952</v>
+      </c>
+      <c r="B883" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C883" s="9"/>
+      <c r="D883" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E883" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="F883" s="9" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G883" s="9" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H883" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I883" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J883" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="K883" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L883" s="10"/>
+      <c r="M883" s="10"/>
+      <c r="N883" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O883" s="11" t="n">
+        <v>46237.444415822</v>
+      </c>
+      <c r="P883" s="9" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q883" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="R883" s="12" t="n">
+        <v>113218.2</v>
+      </c>
+      <c r="S883" s="12" t="n">
+        <v>107611.2</v>
+      </c>
+      <c r="T883" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="884" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A884" s="3" t="n">
+        <v>953</v>
+      </c>
+      <c r="B884" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C884" s="4"/>
+      <c r="D884" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E884" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F884" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="G884" s="4" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H884" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I884" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="J884" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="K884" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="L884" s="5"/>
+      <c r="M884" s="5"/>
+      <c r="N884" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O884" s="6" t="n">
+        <v>46237.450804167</v>
+      </c>
+      <c r="P884" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q884" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="R884" s="7" t="n">
+        <v>38854.2</v>
+      </c>
+      <c r="S884" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T884" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="885" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A885" s="8" t="n">
+        <v>954</v>
+      </c>
+      <c r="B885" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C885" s="9"/>
+      <c r="D885" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E885" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F885" s="9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G885" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H885" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I885" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J885" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K885" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="L885" s="10"/>
+      <c r="M885" s="10"/>
+      <c r="N885" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O885" s="11" t="n">
+        <v>46237.453498843</v>
+      </c>
+      <c r="P885" s="9" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q885" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R885" s="12" t="n">
+        <v>443.44</v>
+      </c>
+      <c r="S885" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T885" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="886" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A886" s="3" t="n">
+        <v>955</v>
+      </c>
+      <c r="B886" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C886" s="4"/>
+      <c r="D886" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E886" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F886" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G886" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H886" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I886" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="J886" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="K886" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="L886" s="5"/>
+      <c r="M886" s="5"/>
+      <c r="N886" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O886" s="6" t="n">
+        <v>46237.455918553</v>
+      </c>
+      <c r="P886" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q886" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R886" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S886" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T886" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="887" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A887" s="8" t="n">
+        <v>956</v>
+      </c>
+      <c r="B887" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C887" s="9"/>
+      <c r="D887" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E887" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F887" s="9" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G887" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="H887" s="10" t="n">
+        <v>46233</v>
+      </c>
+      <c r="I887" s="9" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J887" s="9" t="s">
+        <v>1612</v>
+      </c>
+      <c r="K887" s="9" t="s">
+        <v>1613</v>
+      </c>
+      <c r="L887" s="10"/>
+      <c r="M887" s="10"/>
+      <c r="N887" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O887" s="11" t="n">
+        <v>46237.457760648</v>
+      </c>
+      <c r="P887" s="9" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q887" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="R887" s="12" t="n">
+        <v>19761.36</v>
+      </c>
+      <c r="S887" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T887" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="888" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A888" s="3" t="n">
+        <v>957</v>
+      </c>
+      <c r="B888" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C888" s="4"/>
+      <c r="D888" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E888" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F888" s="4" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G888" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H888" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="I888" s="4" t="s">
+        <v>1746</v>
+      </c>
+      <c r="J888" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K888" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="L888" s="5"/>
+      <c r="M888" s="5"/>
+      <c r="N888" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="O888" s="6" t="n">
+        <v>46237.460359178</v>
+      </c>
+      <c r="P888" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Q888" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R888" s="7" t="n">
+        <v>72000</v>
+      </c>
+      <c r="S888" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T888" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="889" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A889" s="13" t="n">
+        <v>887</v>
+      </c>
+      <c r="B889" s="14"/>
+      <c r="C889" s="14"/>
+      <c r="D889" s="14"/>
+      <c r="E889" s="14"/>
+      <c r="F889" s="14"/>
+      <c r="G889" s="14"/>
+      <c r="H889" s="14"/>
+      <c r="I889" s="14"/>
+      <c r="J889" s="14"/>
+      <c r="K889" s="14"/>
+      <c r="L889" s="14"/>
+      <c r="M889" s="14"/>
+      <c r="N889" s="14"/>
+      <c r="O889" s="14"/>
+      <c r="P889" s="14"/>
+      <c r="Q889" s="14"/>
+      <c r="R889" s="15" t="n">
+        <v>55927450.6926</v>
+      </c>
+      <c r="S889" s="15" t="n">
+        <v>53829921.9706</v>
+      </c>
+      <c r="T889" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="1898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="1897">
   <si>
     <t>ID</t>
   </si>
@@ -5362,9 +5362,6 @@
   </si>
   <si>
     <t>12.418.191/0001-95</t>
-  </si>
-  <si>
-    <t>93 %</t>
   </si>
   <si>
     <t>1085</t>
@@ -55556,13 +55553,13 @@
         <v>23</v>
       </c>
       <c r="E856" s="3" t="s">
-        <v>1783</v>
+        <v>915</v>
       </c>
       <c r="F856" s="4" t="s">
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55594,7 +55591,7 @@
         <v>336168</v>
       </c>
       <c r="S856" s="7" t="n">
-        <v>312156</v>
+        <v>321264</v>
       </c>
       <c r="T856" s="4" t="s">
         <v>32</v>
@@ -55620,7 +55617,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -55678,7 +55675,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -55736,7 +55733,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -55791,10 +55788,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G860" s="4" t="s">
         <v>1788</v>
-      </c>
-      <c r="G860" s="4" t="s">
-        <v>1789</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -55846,25 +55843,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F861" s="9" t="s">
         <v>1790</v>
       </c>
-      <c r="F861" s="9" t="s">
+      <c r="G861" s="9" t="s">
         <v>1791</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1792</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1792</v>
+      </c>
+      <c r="J861" s="9" t="s">
         <v>1793</v>
       </c>
-      <c r="J861" s="9" t="s">
+      <c r="K861" s="9" t="s">
         <v>1794</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1795</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -55907,22 +55904,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="G862" s="4" t="s">
         <v>1796</v>
-      </c>
-      <c r="G862" s="4" t="s">
-        <v>1797</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="J862" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1798</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1799</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -55968,7 +55965,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56026,7 +56023,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56081,22 +56078,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G865" s="9" t="s">
         <v>1802</v>
-      </c>
-      <c r="G865" s="9" t="s">
-        <v>1803</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="J865" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K865" s="9" t="s">
         <v>1804</v>
-      </c>
-      <c r="J865" s="9" t="s">
-        <v>1804</v>
-      </c>
-      <c r="K865" s="9" t="s">
-        <v>1805</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56142,7 +56139,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56200,7 +56197,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56258,7 +56255,7 @@
         <v>1550</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56316,7 +56313,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56371,10 +56368,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G870" s="4" t="s">
         <v>1810</v>
-      </c>
-      <c r="G870" s="4" t="s">
-        <v>1811</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56432,7 +56429,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56490,7 +56487,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56548,7 +56545,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56606,7 +56603,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56664,7 +56661,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -56716,13 +56713,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F876" s="4" t="s">
         <v>1817</v>
       </c>
-      <c r="F876" s="4" t="s">
+      <c r="G876" s="4" t="s">
         <v>1818</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1819</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -56780,7 +56777,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -56838,7 +56835,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -56896,7 +56893,7 @@
         <v>1475</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -56951,22 +56948,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G880" s="4" t="s">
         <v>1823</v>
-      </c>
-      <c r="G880" s="4" t="s">
-        <v>1824</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="J880" s="4" t="s">
         <v>1825</v>
       </c>
-      <c r="J880" s="4" t="s">
+      <c r="K880" s="4" t="s">
         <v>1826</v>
-      </c>
-      <c r="K880" s="4" t="s">
-        <v>1827</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57006,13 +57003,13 @@
         <v>23</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F881" s="9" t="s">
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57070,7 +57067,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57128,7 +57125,7 @@
         <v>1497</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57180,13 +57177,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57241,10 +57238,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57302,7 +57299,7 @@
         <v>1379</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57360,7 +57357,7 @@
         <v>1610</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
@@ -57418,7 +57415,7 @@
         <v>1739</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
@@ -57476,7 +57473,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57534,7 +57531,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57592,7 +57589,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -57650,7 +57647,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -57708,7 +57705,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -57766,7 +57763,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -57824,7 +57821,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -57879,22 +57876,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="G896" s="4" t="s">
         <v>1845</v>
-      </c>
-      <c r="G896" s="4" t="s">
-        <v>1846</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="J896" s="4" t="s">
         <v>1847</v>
       </c>
-      <c r="J896" s="4" t="s">
+      <c r="K896" s="4" t="s">
         <v>1848</v>
-      </c>
-      <c r="K896" s="4" t="s">
-        <v>1849</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -57917,7 +57914,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -57937,22 +57934,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
+        <v>1846</v>
+      </c>
+      <c r="J897" s="9" t="s">
         <v>1847</v>
       </c>
-      <c r="J897" s="9" t="s">
+      <c r="K897" s="9" t="s">
         <v>1848</v>
-      </c>
-      <c r="K897" s="9" t="s">
-        <v>1849</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -57975,7 +57972,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -57998,7 +57995,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58056,7 +58053,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58114,7 +58111,7 @@
         <v>1490</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58172,7 +58169,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58230,7 +58227,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58285,22 +58282,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G903" s="9" t="s">
         <v>1857</v>
-      </c>
-      <c r="G903" s="9" t="s">
-        <v>1858</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="J903" s="9" t="s">
+        <v>1858</v>
+      </c>
+      <c r="K903" s="9" t="s">
         <v>1859</v>
-      </c>
-      <c r="K903" s="9" t="s">
-        <v>1860</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58346,7 +58343,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58404,7 +58401,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58462,7 +58459,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58520,7 +58517,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58578,7 +58575,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -58636,7 +58633,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -58694,7 +58691,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -58752,7 +58749,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -58810,7 +58807,7 @@
         <v>1677</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
@@ -58862,25 +58859,25 @@
         <v>23</v>
       </c>
       <c r="E913" s="8" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F913" s="9" t="s">
         <v>1870</v>
       </c>
-      <c r="F913" s="9" t="s">
+      <c r="G913" s="9" t="s">
         <v>1871</v>
-      </c>
-      <c r="G913" s="9" t="s">
-        <v>1872</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="J913" s="9" t="s">
+        <v>1872</v>
+      </c>
+      <c r="K913" s="9" t="s">
         <v>1873</v>
-      </c>
-      <c r="K913" s="9" t="s">
-        <v>1874</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -58926,7 +58923,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -58984,7 +58981,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59042,7 +59039,7 @@
         <v>1508</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
@@ -59100,7 +59097,7 @@
         <v>1475</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59158,7 +59155,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59216,7 +59213,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59274,7 +59271,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59332,7 +59329,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59390,7 +59387,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59445,22 +59442,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G923" s="9" t="s">
         <v>1884</v>
-      </c>
-      <c r="G923" s="9" t="s">
-        <v>1885</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="J923" s="9" t="s">
+        <v>1885</v>
+      </c>
+      <c r="K923" s="9" t="s">
         <v>1886</v>
-      </c>
-      <c r="K923" s="9" t="s">
-        <v>1887</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59506,7 +59503,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59564,7 +59561,7 @@
         <v>1428</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -59622,7 +59619,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -59674,13 +59671,13 @@
         <v>23</v>
       </c>
       <c r="E927" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F927" s="9" t="s">
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -59697,7 +59694,7 @@
       <c r="L927" s="10"/>
       <c r="M927" s="10"/>
       <c r="N927" s="9" t="s">
-        <v>1576</v>
+        <v>29</v>
       </c>
       <c r="O927" s="11" t="n">
         <v>46255.558190197</v>
@@ -59712,7 +59709,7 @@
         <v>6402.24</v>
       </c>
       <c r="S927" s="12" t="n">
-        <v>0</v>
+        <v>6402.24</v>
       </c>
       <c r="T927" s="9" t="s">
         <v>32</v>
@@ -59732,13 +59729,13 @@
         <v>23</v>
       </c>
       <c r="E928" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F928" s="4" t="s">
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -59755,7 +59752,7 @@
       <c r="L928" s="5"/>
       <c r="M928" s="5"/>
       <c r="N928" s="4" t="s">
-        <v>1576</v>
+        <v>29</v>
       </c>
       <c r="O928" s="6" t="n">
         <v>46255.559634954</v>
@@ -59770,7 +59767,7 @@
         <v>6670.08</v>
       </c>
       <c r="S928" s="7" t="n">
-        <v>0</v>
+        <v>6670.08</v>
       </c>
       <c r="T928" s="4" t="s">
         <v>32</v>
@@ -59790,30 +59787,30 @@
         <v>23</v>
       </c>
       <c r="E929" s="8" t="s">
-        <v>285</v>
+        <v>1869</v>
       </c>
       <c r="F929" s="9" t="s">
+        <v>1892</v>
+      </c>
+      <c r="G929" s="9" t="s">
         <v>1893</v>
-      </c>
-      <c r="G929" s="9" t="s">
-        <v>1894</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="J929" s="9" t="s">
+        <v>1894</v>
+      </c>
+      <c r="K929" s="9" t="s">
         <v>1895</v>
-      </c>
-      <c r="K929" s="9" t="s">
-        <v>1896</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
       <c r="N929" s="9" t="s">
-        <v>1576</v>
+        <v>1288</v>
       </c>
       <c r="O929" s="11" t="n">
         <v>46255.566605324</v>
@@ -59822,13 +59819,13 @@
         <v>1456</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
       </c>
       <c r="S929" s="12" t="n">
-        <v>0</v>
+        <v>69960.68</v>
       </c>
       <c r="T929" s="9" t="s">
         <v>88</v>
@@ -59860,7 +59857,7 @@
         <v>57001333.3226</v>
       </c>
       <c r="S930" s="15" t="n">
-        <v>56038789.5726</v>
+        <v>56130930.5726</v>
       </c>
       <c r="T930" s="14"/>
       <c r="U930" s="14"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -705,6 +705,9 @@
     <t>96.845.896/0001-89</t>
   </si>
   <si>
+    <t>54 %</t>
+  </si>
+  <si>
     <t>MEDKA HOSPITALAR</t>
   </si>
   <si>
@@ -741,7 +744,7 @@
     <t>1171</t>
   </si>
   <si>
-    <t>42 %</t>
+    <t>70 %</t>
   </si>
   <si>
     <t>ALLFAMED COMERCIO</t>
@@ -754,6 +757,90 @@
   </si>
   <si>
     <t>31.187.918/0001-15</t>
+  </si>
+  <si>
+    <t>91 %</t>
+  </si>
+  <si>
+    <t>PBMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>PBMED DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>11.323.800/0001-60</t>
+  </si>
+  <si>
+    <t>ENDOMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>ENDOMED COMERCIO E REPRES DE MEDIC LTDA</t>
+  </si>
+  <si>
+    <t>70.104.344/0001-26</t>
+  </si>
+  <si>
+    <t>S&amp;J DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>S&amp;J DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>55.953.399/0001-17</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>PB FARMA</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>PB FARMA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>05.487.170/0001-66</t>
+  </si>
+  <si>
+    <t>EUROMED HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>EUROMED COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>27.985.664/0001-03</t>
+  </si>
+  <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>FELM</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>FELM - COMERCIO DE MEDICAMENTOS E MATERIAIS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>FELM - COMERCIO DE MEDICAMENTOS E MATERIAIS HOSPIT</t>
+  </si>
+  <si>
+    <t>55.009.085/0001-60</t>
   </si>
 </sst>
 </file>
@@ -947,7 +1034,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -4071,30 +4158,30 @@
         <v>23</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="4" t="s">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="O54" s="6" t="n">
         <v>46260.465283762</v>
@@ -4109,7 +4196,7 @@
         <v>66983</v>
       </c>
       <c r="S54" s="7" t="n">
-        <v>0</v>
+        <v>35894</v>
       </c>
       <c r="T54" s="4" t="s">
         <v>158</v>
@@ -4129,13 +4216,13 @@
         <v>23</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H55" s="11" t="n">
         <v>46259.50275463</v>
@@ -4152,7 +4239,7 @@
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="9" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="O55" s="11" t="n">
         <v>46260.472780787</v>
@@ -4167,7 +4254,7 @@
         <v>10098</v>
       </c>
       <c r="S55" s="12" t="n">
-        <v>0</v>
+        <v>10098</v>
       </c>
       <c r="T55" s="9" t="s">
         <v>32</v>
@@ -4190,22 +4277,22 @@
         <v>218</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
@@ -4251,7 +4338,7 @@
         <v>72</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H57" s="11" t="n">
         <v>46259.659039352</v>
@@ -4303,13 +4390,13 @@
         <v>23</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>184</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>46259.757233796</v>
@@ -4326,7 +4413,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="4" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="O58" s="6" t="n">
         <v>46260.481702546</v>
@@ -4341,7 +4428,7 @@
         <v>21561.88</v>
       </c>
       <c r="S58" s="7" t="n">
-        <v>0</v>
+        <v>21561.88</v>
       </c>
       <c r="T58" s="4" t="s">
         <v>32</v>
@@ -4361,25 +4448,25 @@
         <v>23</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H59" s="11" t="n">
         <v>46259.670231481</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L59" s="10"/>
       <c r="M59" s="10"/>
@@ -4399,7 +4486,7 @@
         <v>104860</v>
       </c>
       <c r="S59" s="12" t="n">
-        <v>44284.2</v>
+        <v>73417</v>
       </c>
       <c r="T59" s="9" t="s">
         <v>32</v>
@@ -4407,35 +4494,499 @@
       <c r="U59" s="9"/>
       <c r="V59" s="9"/>
     </row>
-    <row r="60" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A60" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="15" t="n">
-        <v>1743259.39</v>
-      </c>
-      <c r="S60" s="15" t="n">
-        <v>1414054.51</v>
-      </c>
-      <c r="T60" s="14"/>
-      <c r="U60" s="14"/>
-      <c r="V60" s="16"/>
+    <row r="60" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A60" s="3" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>46261.456944444</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>46261.555533102</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>22323.5</v>
+      </c>
+      <c r="S60" s="7" t="n">
+        <v>20250</v>
+      </c>
+      <c r="T60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+    </row>
+    <row r="61" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A61" s="8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>46260.641412037</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O61" s="11" t="n">
+        <v>46261.563297998</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q61" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R61" s="12" t="n">
+        <v>8857.2</v>
+      </c>
+      <c r="S61" s="12" t="n">
+        <v>8857.2</v>
+      </c>
+      <c r="T61" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+    </row>
+    <row r="62" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A62" s="3" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>46261.627002315</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>46262.58220772</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R62" s="7" t="n">
+        <v>9240</v>
+      </c>
+      <c r="S62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+    </row>
+    <row r="63" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A63" s="8" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>46261.674166667</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O63" s="11" t="n">
+        <v>46262.58240625</v>
+      </c>
+      <c r="P63" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q63" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R63" s="12" t="n">
+        <v>42336</v>
+      </c>
+      <c r="S63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U63" s="9"/>
+      <c r="V63" s="9"/>
+    </row>
+    <row r="64" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A64" s="3" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>46261.624131944</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O64" s="6" t="n">
+        <v>46262.582538507</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q64" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R64" s="7" t="n">
+        <v>44352</v>
+      </c>
+      <c r="S64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+    </row>
+    <row r="65" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A65" s="8" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>46261.626898148</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O65" s="11" t="n">
+        <v>46262.582696609</v>
+      </c>
+      <c r="P65" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q65" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R65" s="12" t="n">
+        <v>5972</v>
+      </c>
+      <c r="S65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U65" s="9"/>
+      <c r="V65" s="9"/>
+    </row>
+    <row r="66" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A66" s="3" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O66" s="6" t="n">
+        <v>46262.59088912</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q66" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="R66" s="7" t="n">
+        <v>5346</v>
+      </c>
+      <c r="S66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+    </row>
+    <row r="67" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A67" s="8" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H67" s="10" t="n">
+        <v>46261</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O67" s="11" t="n">
+        <v>46262.592242708</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q67" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="R67" s="12" t="n">
+        <v>3650.4</v>
+      </c>
+      <c r="S67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U67" s="9"/>
+      <c r="V67" s="9"/>
+    </row>
+    <row r="68" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A68" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
+      <c r="P68" s="14"/>
+      <c r="Q68" s="14"/>
+      <c r="R68" s="15" t="n">
+        <v>1885336.49</v>
+      </c>
+      <c r="S68" s="15" t="n">
+        <v>1539848.39</v>
+      </c>
+      <c r="T68" s="14"/>
+      <c r="U68" s="14"/>
+      <c r="V68" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="1928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="1950">
   <si>
     <t>ID</t>
   </si>
@@ -5364,9 +5364,6 @@
     <t>12.418.191/0001-95</t>
   </si>
   <si>
-    <t>98 %</t>
-  </si>
-  <si>
     <t>1085</t>
   </si>
   <si>
@@ -5499,9 +5496,6 @@
     <t>20.001.049/0001-76</t>
   </si>
   <si>
-    <t>62 %</t>
-  </si>
-  <si>
     <t>1111</t>
   </si>
   <si>
@@ -5760,9 +5754,6 @@
     <t>1171</t>
   </si>
   <si>
-    <t>70 %</t>
-  </si>
-  <si>
     <t>1173</t>
   </si>
   <si>
@@ -5797,6 +5788,81 @@
   </si>
   <si>
     <t>1183</t>
+  </si>
+  <si>
+    <t>7 %</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>48 %</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>15 %</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>ODONTOMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>DENTAL CENTRO OESTE</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>DCO COMERCIO DE PRODUTOS PARA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>36.900.926/0001-80</t>
+  </si>
+  <si>
+    <t>DU BOM DIST.</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR </t>
+  </si>
+  <si>
+    <t>18.483.775/0001-20</t>
+  </si>
+  <si>
+    <t>1197</t>
   </si>
 </sst>
 </file>
@@ -5990,7 +6056,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V950"/>
+  <dimension ref="A1:V964"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -55646,13 +55712,13 @@
         <v>23</v>
       </c>
       <c r="E856" s="3" t="s">
-        <v>1783</v>
+        <v>24</v>
       </c>
       <c r="F856" s="4" t="s">
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55669,7 +55735,7 @@
       <c r="L856" s="5"/>
       <c r="M856" s="5"/>
       <c r="N856" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O856" s="6" t="n">
         <v>46232.365431516</v>
@@ -55684,7 +55750,7 @@
         <v>336168</v>
       </c>
       <c r="S856" s="7" t="n">
-        <v>330372</v>
+        <v>336168</v>
       </c>
       <c r="T856" s="4" t="s">
         <v>32</v>
@@ -55710,7 +55776,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -55768,7 +55834,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -55826,7 +55892,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -55881,10 +55947,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G860" s="4" t="s">
         <v>1788</v>
-      </c>
-      <c r="G860" s="4" t="s">
-        <v>1789</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -55936,25 +56002,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F861" s="9" t="s">
         <v>1790</v>
       </c>
-      <c r="F861" s="9" t="s">
+      <c r="G861" s="9" t="s">
         <v>1791</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1792</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1792</v>
+      </c>
+      <c r="J861" s="9" t="s">
         <v>1793</v>
       </c>
-      <c r="J861" s="9" t="s">
+      <c r="K861" s="9" t="s">
         <v>1794</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1795</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -55997,22 +56063,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="G862" s="4" t="s">
         <v>1796</v>
-      </c>
-      <c r="G862" s="4" t="s">
-        <v>1797</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="J862" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1798</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1799</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56058,7 +56124,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56116,7 +56182,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56171,22 +56237,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G865" s="9" t="s">
         <v>1802</v>
-      </c>
-      <c r="G865" s="9" t="s">
-        <v>1803</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="J865" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K865" s="9" t="s">
         <v>1804</v>
-      </c>
-      <c r="J865" s="9" t="s">
-        <v>1804</v>
-      </c>
-      <c r="K865" s="9" t="s">
-        <v>1805</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56232,7 +56298,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56290,7 +56356,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56348,7 +56414,7 @@
         <v>1549</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56406,7 +56472,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56461,10 +56527,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G870" s="4" t="s">
         <v>1810</v>
-      </c>
-      <c r="G870" s="4" t="s">
-        <v>1811</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56522,7 +56588,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56580,7 +56646,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56638,7 +56704,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56696,7 +56762,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56754,7 +56820,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -56806,13 +56872,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F876" s="4" t="s">
         <v>1817</v>
       </c>
-      <c r="F876" s="4" t="s">
+      <c r="G876" s="4" t="s">
         <v>1818</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1819</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -56870,7 +56936,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -56928,7 +56994,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -56986,7 +57052,7 @@
         <v>1474</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57041,22 +57107,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G880" s="4" t="s">
         <v>1823</v>
-      </c>
-      <c r="G880" s="4" t="s">
-        <v>1824</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="J880" s="4" t="s">
         <v>1825</v>
       </c>
-      <c r="J880" s="4" t="s">
+      <c r="K880" s="4" t="s">
         <v>1826</v>
-      </c>
-      <c r="K880" s="4" t="s">
-        <v>1827</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57096,13 +57162,13 @@
         <v>23</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>1828</v>
+        <v>1285</v>
       </c>
       <c r="F881" s="9" t="s">
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57134,7 +57200,7 @@
         <v>73636</v>
       </c>
       <c r="S881" s="12" t="n">
-        <v>45349</v>
+        <v>54778</v>
       </c>
       <c r="T881" s="9" t="s">
         <v>32</v>
@@ -57160,7 +57226,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57218,7 +57284,7 @@
         <v>1496</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57270,13 +57336,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57331,10 +57397,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57392,7 +57458,7 @@
         <v>1379</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57450,7 +57516,7 @@
         <v>1608</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
@@ -57508,7 +57574,7 @@
         <v>1739</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
@@ -57566,7 +57632,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57624,7 +57690,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57682,7 +57748,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -57740,7 +57806,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -57798,7 +57864,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -57856,7 +57922,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -57914,7 +57980,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -57969,22 +58035,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="J896" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K896" s="4" t="s">
         <v>1847</v>
-      </c>
-      <c r="J896" s="4" t="s">
-        <v>1848</v>
-      </c>
-      <c r="K896" s="4" t="s">
-        <v>1849</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58007,7 +58073,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58027,22 +58093,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="J897" s="9" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K897" s="9" t="s">
         <v>1847</v>
-      </c>
-      <c r="J897" s="9" t="s">
-        <v>1848</v>
-      </c>
-      <c r="K897" s="9" t="s">
-        <v>1849</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58065,7 +58131,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58088,7 +58154,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58146,7 +58212,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58204,7 +58270,7 @@
         <v>1489</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58262,7 +58328,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58320,7 +58386,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58375,22 +58441,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="G903" s="9" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
+        <v>1855</v>
+      </c>
+      <c r="J903" s="9" t="s">
         <v>1857</v>
       </c>
-      <c r="J903" s="9" t="s">
-        <v>1859</v>
-      </c>
       <c r="K903" s="9" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58436,7 +58502,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58494,7 +58560,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58552,7 +58618,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58610,7 +58676,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58668,7 +58734,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -58726,7 +58792,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -58784,7 +58850,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -58842,7 +58908,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -58900,7 +58966,7 @@
         <v>1676</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
@@ -58952,25 +59018,25 @@
         <v>23</v>
       </c>
       <c r="E913" s="8" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F913" s="9" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G913" s="9" t="s">
         <v>1870</v>
-      </c>
-      <c r="F913" s="9" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G913" s="9" t="s">
-        <v>1872</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
+        <v>1869</v>
+      </c>
+      <c r="J913" s="9" t="s">
         <v>1871</v>
       </c>
-      <c r="J913" s="9" t="s">
-        <v>1873</v>
-      </c>
       <c r="K913" s="9" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -59016,7 +59082,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59074,7 +59140,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59132,7 +59198,7 @@
         <v>1507</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
@@ -59190,7 +59256,7 @@
         <v>1474</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59248,7 +59314,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59306,7 +59372,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59364,7 +59430,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59422,7 +59488,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59480,7 +59546,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59535,22 +59601,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="G923" s="9" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
+        <v>1882</v>
+      </c>
+      <c r="J923" s="9" t="s">
         <v>1884</v>
       </c>
-      <c r="J923" s="9" t="s">
-        <v>1886</v>
-      </c>
       <c r="K923" s="9" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59596,7 +59662,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59654,7 +59720,7 @@
         <v>1428</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -59712,7 +59778,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -59770,7 +59836,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -59828,7 +59894,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -59883,22 +59949,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="G929" s="9" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
+        <v>1891</v>
+      </c>
+      <c r="J929" s="9" t="s">
         <v>1893</v>
       </c>
-      <c r="J929" s="9" t="s">
-        <v>1895</v>
-      </c>
       <c r="K929" s="9" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -59912,7 +59978,7 @@
         <v>1456</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -59944,7 +60010,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60002,7 +60068,7 @@
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60060,7 +60126,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60118,7 +60184,7 @@
         <v>1460</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
@@ -60170,25 +60236,25 @@
         <v>23</v>
       </c>
       <c r="E934" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F934" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G934" s="4" t="s">
         <v>1902</v>
-      </c>
-      <c r="F934" s="4" t="s">
-        <v>1903</v>
-      </c>
-      <c r="G934" s="4" t="s">
-        <v>1904</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="J934" s="4" t="s">
         <v>1903</v>
       </c>
-      <c r="J934" s="4" t="s">
-        <v>1905</v>
-      </c>
       <c r="K934" s="4" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
@@ -60234,7 +60300,7 @@
         <v>1060</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60286,30 +60352,30 @@
         <v>23</v>
       </c>
       <c r="E936" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
+        <v>1908</v>
+      </c>
+      <c r="J936" s="4" t="s">
+        <v>1909</v>
+      </c>
+      <c r="K936" s="4" t="s">
         <v>1910</v>
-      </c>
-      <c r="J936" s="4" t="s">
-        <v>1911</v>
-      </c>
-      <c r="K936" s="4" t="s">
-        <v>1912</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
       <c r="N936" s="4" t="s">
-        <v>1575</v>
+        <v>29</v>
       </c>
       <c r="O936" s="6" t="n">
         <v>46260.475690625</v>
@@ -60318,13 +60384,13 @@
         <v>1456</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
       </c>
       <c r="S936" s="7" t="n">
-        <v>0</v>
+        <v>42572</v>
       </c>
       <c r="T936" s="4" t="s">
         <v>88</v>
@@ -60350,7 +60416,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60408,7 +60474,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60460,13 +60526,13 @@
         <v>23</v>
       </c>
       <c r="E939" s="8" t="s">
-        <v>1915</v>
+        <v>24</v>
       </c>
       <c r="F939" s="9" t="s">
         <v>945</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60483,7 +60549,7 @@
       <c r="L939" s="10"/>
       <c r="M939" s="10"/>
       <c r="N939" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O939" s="11" t="n">
         <v>46260.610262269</v>
@@ -60498,7 +60564,7 @@
         <v>104860</v>
       </c>
       <c r="S939" s="12" t="n">
-        <v>73417</v>
+        <v>104860</v>
       </c>
       <c r="T939" s="9" t="s">
         <v>32</v>
@@ -60524,7 +60590,7 @@
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -60582,7 +60648,7 @@
         <v>1549</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -60640,7 +60706,7 @@
         <v>1280</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -60698,7 +60764,7 @@
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -60756,7 +60822,7 @@
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60814,7 +60880,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -60872,7 +60938,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -60930,7 +60996,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -60988,7 +61054,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61040,13 +61106,13 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="F949" s="9" t="s">
         <v>1739</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
@@ -61086,35 +61152,847 @@
       <c r="U949" s="9"/>
       <c r="V949" s="9"/>
     </row>
-    <row r="950" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A950" s="13" t="n">
-        <v>948</v>
-      </c>
-      <c r="B950" s="14"/>
-      <c r="C950" s="14"/>
-      <c r="D950" s="14"/>
-      <c r="E950" s="14"/>
-      <c r="F950" s="14"/>
-      <c r="G950" s="14"/>
-      <c r="H950" s="14"/>
-      <c r="I950" s="14"/>
-      <c r="J950" s="14"/>
-      <c r="K950" s="14"/>
-      <c r="L950" s="14"/>
-      <c r="M950" s="14"/>
-      <c r="N950" s="14"/>
-      <c r="O950" s="14"/>
-      <c r="P950" s="14"/>
-      <c r="Q950" s="14"/>
-      <c r="R950" s="15" t="n">
-        <v>57758802.3026</v>
-      </c>
-      <c r="S950" s="15" t="n">
-        <v>56639972.3326</v>
-      </c>
-      <c r="T950" s="14"/>
-      <c r="U950" s="14"/>
-      <c r="V950" s="16"/>
+    <row r="950" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A950" s="3" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B950" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C950" s="4"/>
+      <c r="D950" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E950" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F950" s="4" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G950" s="4" t="s">
+        <v>1926</v>
+      </c>
+      <c r="H950" s="5" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I950" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J950" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K950" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="L950" s="5"/>
+      <c r="M950" s="5"/>
+      <c r="N950" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O950" s="6" t="n">
+        <v>46266.3342289</v>
+      </c>
+      <c r="P950" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q950" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R950" s="7" t="n">
+        <v>63150.72</v>
+      </c>
+      <c r="S950" s="7" t="n">
+        <v>4224.96</v>
+      </c>
+      <c r="T950" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U950" s="4"/>
+      <c r="V950" s="4"/>
+    </row>
+    <row r="951" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A951" s="8" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B951" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C951" s="9"/>
+      <c r="D951" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E951" s="8" t="s">
+        <v>1927</v>
+      </c>
+      <c r="F951" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="G951" s="9" t="s">
+        <v>1928</v>
+      </c>
+      <c r="H951" s="11" t="n">
+        <v>46265.756805556</v>
+      </c>
+      <c r="I951" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="J951" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="K951" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="L951" s="10"/>
+      <c r="M951" s="10"/>
+      <c r="N951" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O951" s="11" t="n">
+        <v>46266.686144444</v>
+      </c>
+      <c r="P951" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q951" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R951" s="12" t="n">
+        <v>16743.84</v>
+      </c>
+      <c r="S951" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T951" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U951" s="9"/>
+      <c r="V951" s="9"/>
+    </row>
+    <row r="952" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A952" s="3" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B952" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C952" s="4"/>
+      <c r="D952" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E952" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F952" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G952" s="4" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H952" s="6" t="n">
+        <v>46262.6721875</v>
+      </c>
+      <c r="I952" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J952" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K952" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L952" s="5"/>
+      <c r="M952" s="5"/>
+      <c r="N952" s="4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O952" s="6" t="n">
+        <v>46266.68744059</v>
+      </c>
+      <c r="P952" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q952" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R952" s="7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="S952" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T952" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U952" s="4"/>
+      <c r="V952" s="4"/>
+    </row>
+    <row r="953" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A953" s="8" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B953" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C953" s="9"/>
+      <c r="D953" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E953" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F953" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="G953" s="9" t="s">
+        <v>1930</v>
+      </c>
+      <c r="H953" s="11" t="n">
+        <v>46265.738773148</v>
+      </c>
+      <c r="I953" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="J953" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="K953" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="L953" s="10"/>
+      <c r="M953" s="10"/>
+      <c r="N953" s="9" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O953" s="11" t="n">
+        <v>46266.688499306</v>
+      </c>
+      <c r="P953" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q953" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R953" s="12" t="n">
+        <v>26895.14</v>
+      </c>
+      <c r="S953" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T953" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U953" s="9"/>
+      <c r="V953" s="9"/>
+    </row>
+    <row r="954" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A954" s="3" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B954" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C954" s="4"/>
+      <c r="D954" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E954" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F954" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G954" s="4" t="s">
+        <v>1931</v>
+      </c>
+      <c r="H954" s="6" t="n">
+        <v>46265.406400463</v>
+      </c>
+      <c r="I954" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J954" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="K954" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="L954" s="5"/>
+      <c r="M954" s="5"/>
+      <c r="N954" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O954" s="6" t="n">
+        <v>46266.689224306</v>
+      </c>
+      <c r="P954" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q954" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R954" s="7" t="n">
+        <v>14040</v>
+      </c>
+      <c r="S954" s="7" t="n">
+        <v>14040</v>
+      </c>
+      <c r="T954" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U954" s="4"/>
+      <c r="V954" s="4"/>
+    </row>
+    <row r="955" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A955" s="8" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B955" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C955" s="9"/>
+      <c r="D955" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E955" s="8" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F955" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="G955" s="9" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H955" s="11" t="n">
+        <v>46262.643506944</v>
+      </c>
+      <c r="I955" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J955" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K955" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L955" s="10"/>
+      <c r="M955" s="10"/>
+      <c r="N955" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O955" s="11" t="n">
+        <v>46266.690371215</v>
+      </c>
+      <c r="P955" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q955" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R955" s="12" t="n">
+        <v>33757.34</v>
+      </c>
+      <c r="S955" s="12" t="n">
+        <v>4959.12</v>
+      </c>
+      <c r="T955" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U955" s="9"/>
+      <c r="V955" s="9"/>
+    </row>
+    <row r="956" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A956" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B956" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C956" s="4"/>
+      <c r="D956" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E956" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F956" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="G956" s="4" t="s">
+        <v>1934</v>
+      </c>
+      <c r="H956" s="6" t="n">
+        <v>46262.644305556</v>
+      </c>
+      <c r="I956" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="J956" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="K956" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="L956" s="5"/>
+      <c r="M956" s="5"/>
+      <c r="N956" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O956" s="6" t="n">
+        <v>46266.691768252</v>
+      </c>
+      <c r="P956" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q956" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="R956" s="7" t="n">
+        <v>30650</v>
+      </c>
+      <c r="S956" s="7" t="n">
+        <v>30650</v>
+      </c>
+      <c r="T956" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U956" s="4"/>
+      <c r="V956" s="4"/>
+    </row>
+    <row r="957" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A957" s="8" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B957" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C957" s="9"/>
+      <c r="D957" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E957" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F957" s="9" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G957" s="9" t="s">
+        <v>1935</v>
+      </c>
+      <c r="H957" s="11" t="n">
+        <v>46262.617488426</v>
+      </c>
+      <c r="I957" s="9" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J957" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="K957" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L957" s="10"/>
+      <c r="M957" s="10"/>
+      <c r="N957" s="9" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O957" s="11" t="n">
+        <v>46266.693244294</v>
+      </c>
+      <c r="P957" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q957" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R957" s="12" t="n">
+        <v>32787.96</v>
+      </c>
+      <c r="S957" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T957" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="U957" s="9"/>
+      <c r="V957" s="9"/>
+    </row>
+    <row r="958" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A958" s="3" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B958" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C958" s="4"/>
+      <c r="D958" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E958" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F958" s="4" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G958" s="4" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H958" s="6" t="n">
+        <v>46262.337835648</v>
+      </c>
+      <c r="I958" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J958" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K958" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L958" s="5"/>
+      <c r="M958" s="5"/>
+      <c r="N958" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O958" s="6" t="n">
+        <v>46266.694431794</v>
+      </c>
+      <c r="P958" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q958" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R958" s="7" t="n">
+        <v>18480.04</v>
+      </c>
+      <c r="S958" s="7" t="n">
+        <v>18480.04</v>
+      </c>
+      <c r="T958" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U958" s="4"/>
+      <c r="V958" s="4"/>
+    </row>
+    <row r="959" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A959" s="8" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B959" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C959" s="9"/>
+      <c r="D959" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E959" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F959" s="9" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G959" s="9" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H959" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I959" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="J959" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K959" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L959" s="10"/>
+      <c r="M959" s="10"/>
+      <c r="N959" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O959" s="11" t="n">
+        <v>46266.695900926</v>
+      </c>
+      <c r="P959" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q959" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R959" s="12" t="n">
+        <v>8262</v>
+      </c>
+      <c r="S959" s="12" t="n">
+        <v>8262</v>
+      </c>
+      <c r="T959" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U959" s="9"/>
+      <c r="V959" s="9"/>
+    </row>
+    <row r="960" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A960" s="3" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B960" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C960" s="4"/>
+      <c r="D960" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E960" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F960" s="4" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G960" s="4" t="s">
+        <v>1939</v>
+      </c>
+      <c r="H960" s="5" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I960" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J960" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K960" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L960" s="5"/>
+      <c r="M960" s="5"/>
+      <c r="N960" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O960" s="6" t="n">
+        <v>46266.697281597</v>
+      </c>
+      <c r="P960" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q960" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R960" s="7" t="n">
+        <v>4847.04</v>
+      </c>
+      <c r="S960" s="7" t="n">
+        <v>4847.04</v>
+      </c>
+      <c r="T960" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U960" s="4"/>
+      <c r="V960" s="4"/>
+    </row>
+    <row r="961" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A961" s="8" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B961" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C961" s="9"/>
+      <c r="D961" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E961" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F961" s="9" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G961" s="9" t="s">
+        <v>1941</v>
+      </c>
+      <c r="H961" s="10" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I961" s="9" t="s">
+        <v>1940</v>
+      </c>
+      <c r="J961" s="9" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K961" s="9" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L961" s="10"/>
+      <c r="M961" s="10"/>
+      <c r="N961" s="9" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O961" s="11" t="n">
+        <v>46266.698305127</v>
+      </c>
+      <c r="P961" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q961" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="R961" s="12" t="n">
+        <v>17437.2</v>
+      </c>
+      <c r="S961" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T961" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="U961" s="9"/>
+      <c r="V961" s="9"/>
+    </row>
+    <row r="962" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A962" s="3" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B962" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C962" s="4"/>
+      <c r="D962" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E962" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F962" s="4" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G962" s="4" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H962" s="5" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I962" s="4" t="s">
+        <v>1946</v>
+      </c>
+      <c r="J962" s="4" t="s">
+        <v>1947</v>
+      </c>
+      <c r="K962" s="4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="L962" s="5"/>
+      <c r="M962" s="5"/>
+      <c r="N962" s="4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O962" s="6" t="n">
+        <v>46266.700271262</v>
+      </c>
+      <c r="P962" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q962" s="4" t="s">
+        <v>1895</v>
+      </c>
+      <c r="R962" s="7" t="n">
+        <v>10074</v>
+      </c>
+      <c r="S962" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T962" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U962" s="4"/>
+      <c r="V962" s="4"/>
+    </row>
+    <row r="963" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A963" s="8" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B963" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C963" s="9"/>
+      <c r="D963" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E963" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F963" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="G963" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H963" s="11" t="n">
+        <v>46267.438217593</v>
+      </c>
+      <c r="I963" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J963" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K963" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L963" s="10"/>
+      <c r="M963" s="10"/>
+      <c r="N963" s="9" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O963" s="11" t="n">
+        <v>46267.661274965</v>
+      </c>
+      <c r="P963" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q963" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R963" s="12" t="n">
+        <v>14178</v>
+      </c>
+      <c r="S963" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T963" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U963" s="9"/>
+      <c r="V963" s="9"/>
+    </row>
+    <row r="964" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A964" s="13" t="n">
+        <v>962</v>
+      </c>
+      <c r="B964" s="14"/>
+      <c r="C964" s="14"/>
+      <c r="D964" s="14"/>
+      <c r="E964" s="14"/>
+      <c r="F964" s="14"/>
+      <c r="G964" s="14"/>
+      <c r="H964" s="14"/>
+      <c r="I964" s="14"/>
+      <c r="J964" s="14"/>
+      <c r="K964" s="14"/>
+      <c r="L964" s="14"/>
+      <c r="M964" s="14"/>
+      <c r="N964" s="14"/>
+      <c r="O964" s="14"/>
+      <c r="P964" s="14"/>
+      <c r="Q964" s="14"/>
+      <c r="R964" s="15" t="n">
+        <v>58094105.5826</v>
+      </c>
+      <c r="S964" s="15" t="n">
+        <v>56822675.4926</v>
+      </c>
+      <c r="T964" s="14"/>
+      <c r="U964" s="14"/>
+      <c r="V964" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>
